--- a/database/event/8041/event_8041_evp_summary.xlsx
+++ b/database/event/8041/event_8041_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>11.0577</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>6.6872</v>
       </c>
       <c r="D2" t="n">
         <v>4.0457</v>
@@ -545,7 +545,7 @@
         <v>8.2835</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5.0095</v>
       </c>
       <c r="D3" t="n">
         <v>2.925</v>
@@ -591,7 +591,7 @@
         <v>7.757</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.6911</v>
       </c>
       <c r="D4" t="n">
         <v>2.7123</v>
@@ -637,7 +637,7 @@
         <v>6.9378</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4.1957</v>
       </c>
       <c r="D5" t="n">
         <v>2.3814</v>
@@ -683,7 +683,7 @@
         <v>6.075</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3.6739</v>
       </c>
       <c r="D6" t="n">
         <v>2.0328</v>
@@ -729,7 +729,7 @@
         <v>5.3715</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3.2485</v>
       </c>
       <c r="D7" t="n">
         <v>1.7486</v>
@@ -775,7 +775,7 @@
         <v>5.3357</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3.2268</v>
       </c>
       <c r="D8" t="n">
         <v>1.7341</v>
@@ -821,7 +821,7 @@
         <v>5.1469</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3.1126</v>
       </c>
       <c r="D9" t="n">
         <v>1.6579</v>
@@ -867,7 +867,7 @@
         <v>5.1033</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>3.0863</v>
       </c>
       <c r="D10" t="n">
         <v>1.6403</v>
@@ -913,7 +913,7 @@
         <v>5.0053</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>3.027</v>
       </c>
       <c r="D11" t="n">
         <v>1.6007</v>
@@ -959,7 +959,7 @@
         <v>4.5982</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.7808</v>
       </c>
       <c r="D12" t="n">
         <v>1.4362</v>
@@ -1005,7 +1005,7 @@
         <v>4.5971</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.7801</v>
       </c>
       <c r="D13" t="n">
         <v>1.4358</v>
@@ -1051,7 +1051,7 @@
         <v>4.3633</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2.6387</v>
       </c>
       <c r="D14" t="n">
         <v>1.3413</v>
@@ -1097,7 +1097,7 @@
         <v>4.0867</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2.4715</v>
       </c>
       <c r="D15" t="n">
         <v>1.2296</v>
@@ -1143,7 +1143,7 @@
         <v>3.8553</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.3315</v>
       </c>
       <c r="D16" t="n">
         <v>1.1361</v>
@@ -1189,7 +1189,7 @@
         <v>3.5777</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2.1636</v>
       </c>
       <c r="D17" t="n">
         <v>1.0239</v>
@@ -1235,7 +1235,7 @@
         <v>3.3095</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2.0014</v>
       </c>
       <c r="D18" t="n">
         <v>0.9156</v>
@@ -1281,7 +1281,7 @@
         <v>2.9205</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.7662</v>
       </c>
       <c r="D19" t="n">
         <v>0.7585</v>
@@ -1327,7 +1327,7 @@
         <v>2.7697</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.675</v>
       </c>
       <c r="D20" t="n">
         <v>0.6975</v>
@@ -1373,7 +1373,7 @@
         <v>2.2779</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.3776</v>
       </c>
       <c r="D21" t="n">
         <v>0.4989</v>
@@ -1419,7 +1419,7 @@
         <v>2.1705</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.3126</v>
       </c>
       <c r="D22" t="n">
         <v>0.4555</v>
@@ -1465,7 +1465,7 @@
         <v>2.1447</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="D23" t="n">
         <v>0.445</v>
@@ -1511,7 +1511,7 @@
         <v>2.1376</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.2927</v>
       </c>
       <c r="D24" t="n">
         <v>0.4422</v>
@@ -1557,7 +1557,7 @@
         <v>2.0661</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.2495</v>
       </c>
       <c r="D25" t="n">
         <v>0.4133</v>
@@ -1603,7 +1603,7 @@
         <v>2.0351</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.2307</v>
       </c>
       <c r="D26" t="n">
         <v>0.4008</v>
@@ -1649,7 +1649,7 @@
         <v>1.7936</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.0847</v>
       </c>
       <c r="D27" t="n">
         <v>0.3032</v>
@@ -1695,7 +1695,7 @@
         <v>1.7449</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.0552</v>
       </c>
       <c r="D28" t="n">
         <v>0.2835</v>
@@ -1741,7 +1741,7 @@
         <v>1.64</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.9918</v>
       </c>
       <c r="D29" t="n">
         <v>0.2412</v>
@@ -1787,7 +1787,7 @@
         <v>1.5913</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.9623</v>
       </c>
       <c r="D30" t="n">
         <v>0.2215</v>
@@ -1833,7 +1833,7 @@
         <v>1.322</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.7995</v>
       </c>
       <c r="D31" t="n">
         <v>0.1127</v>
@@ -1879,7 +1879,7 @@
         <v>1.138</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.6882</v>
       </c>
       <c r="D32" t="n">
         <v>0.0384</v>
@@ -1925,7 +1925,7 @@
         <v>1.1211</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.678</v>
       </c>
       <c r="D33" t="n">
         <v>0.0315</v>
@@ -1971,7 +1971,7 @@
         <v>0.7896</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.4775</v>
       </c>
       <c r="D34" t="n">
         <v>-0.1024</v>
@@ -2017,7 +2017,7 @@
         <v>0.7841</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.4742</v>
       </c>
       <c r="D35" t="n">
         <v>-0.1046</v>
@@ -2063,7 +2063,7 @@
         <v>0.7226</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.437</v>
       </c>
       <c r="D36" t="n">
         <v>-0.1294</v>
@@ -2109,7 +2109,7 @@
         <v>0.6688</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.4045</v>
       </c>
       <c r="D37" t="n">
         <v>-0.1512</v>
@@ -2155,7 +2155,7 @@
         <v>0.6414</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.3879</v>
       </c>
       <c r="D38" t="n">
         <v>-0.1623</v>
@@ -2201,7 +2201,7 @@
         <v>0.5917</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.3578</v>
       </c>
       <c r="D39" t="n">
         <v>-0.1823</v>
@@ -2247,7 +2247,7 @@
         <v>0.5578</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
       <c r="D40" t="n">
         <v>-0.196</v>
@@ -2293,7 +2293,7 @@
         <v>0.5507</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="D41" t="n">
         <v>-0.1989</v>
@@ -2339,7 +2339,7 @@
         <v>0.5215</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.3154</v>
       </c>
       <c r="D42" t="n">
         <v>-0.2107</v>
@@ -2385,7 +2385,7 @@
         <v>0.4813</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.2911</v>
       </c>
       <c r="D43" t="n">
         <v>-0.2269</v>
@@ -2431,7 +2431,7 @@
         <v>0.4112</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.2487</v>
       </c>
       <c r="D44" t="n">
         <v>-0.2552</v>
@@ -2477,7 +2477,7 @@
         <v>0.2125</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.1285</v>
       </c>
       <c r="D45" t="n">
         <v>-0.3355</v>
@@ -2523,7 +2523,7 @@
         <v>0.1906</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1153</v>
       </c>
       <c r="D46" t="n">
         <v>-0.3444</v>
@@ -2569,7 +2569,7 @@
         <v>0.1847</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.1117</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3467</v>
@@ -2615,7 +2615,7 @@
         <v>0.1648</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.0997</v>
       </c>
       <c r="D48" t="n">
         <v>-0.3548</v>
@@ -2661,7 +2661,7 @@
         <v>0.1257</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3706</v>
@@ -2707,7 +2707,7 @@
         <v>0.1127</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.0682</v>
       </c>
       <c r="D50" t="n">
         <v>-0.3758</v>
@@ -2753,7 +2753,7 @@
         <v>-0.0497</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.0301</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4414</v>
@@ -2799,7 +2799,7 @@
         <v>-0.129</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.078</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4735</v>
@@ -2845,7 +2845,7 @@
         <v>-0.1731</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.1047</v>
       </c>
       <c r="D53" t="n">
         <v>-0.4913</v>
@@ -2891,7 +2891,7 @@
         <v>-0.2361</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1428</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5167</v>
@@ -2937,7 +2937,7 @@
         <v>-0.2904</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1756</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5387</v>
@@ -2983,7 +2983,7 @@
         <v>-0.2975</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1799</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5415</v>
@@ -3029,7 +3029,7 @@
         <v>-0.303</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.1832</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5438</v>
@@ -3075,7 +3075,7 @@
         <v>-0.3574</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2161</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5657</v>
@@ -3121,7 +3121,7 @@
         <v>-0.3764</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2276</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5734</v>
@@ -3167,7 +3167,7 @@
         <v>-0.3966</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2398</v>
       </c>
       <c r="D60" t="n">
         <v>-0.5816</v>
@@ -3213,7 +3213,7 @@
         <v>-0.4132</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.2499</v>
       </c>
       <c r="D61" t="n">
         <v>-0.5883</v>
@@ -3259,7 +3259,7 @@
         <v>-0.4481</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.271</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6024</v>
@@ -3305,7 +3305,7 @@
         <v>-0.4539</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.2745</v>
       </c>
       <c r="D63" t="n">
         <v>-0.6047</v>
@@ -3351,7 +3351,7 @@
         <v>-0.4762</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.288</v>
       </c>
       <c r="D64" t="n">
         <v>-0.6137</v>
@@ -3397,7 +3397,7 @@
         <v>-0.5331</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.3224</v>
       </c>
       <c r="D65" t="n">
         <v>-0.6367</v>
@@ -3443,7 +3443,7 @@
         <v>-0.7368</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.4456</v>
       </c>
       <c r="D66" t="n">
         <v>-0.719</v>
@@ -3489,7 +3489,7 @@
         <v>-0.8952</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.5414</v>
       </c>
       <c r="D67" t="n">
         <v>-0.783</v>
@@ -3535,7 +3535,7 @@
         <v>-0.9068000000000001</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.5484</v>
       </c>
       <c r="D68" t="n">
         <v>-0.7877</v>
@@ -3581,7 +3581,7 @@
         <v>-0.915</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.5534</v>
       </c>
       <c r="D69" t="n">
         <v>-0.791</v>
@@ -3627,7 +3627,7 @@
         <v>-0.9406</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.5688</v>
       </c>
       <c r="D70" t="n">
         <v>-0.8013</v>
@@ -3673,7 +3673,7 @@
         <v>-0.9462</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.5722</v>
       </c>
       <c r="D71" t="n">
         <v>-0.8036</v>
@@ -3719,7 +3719,7 @@
         <v>-1</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.6048</v>
       </c>
       <c r="D72" t="n">
         <v>-0.8253</v>
@@ -3765,7 +3765,7 @@
         <v>-1.0075</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.6093</v>
       </c>
       <c r="D73" t="n">
         <v>-0.8284</v>
@@ -3811,7 +3811,7 @@
         <v>-1.3911</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.8413</v>
       </c>
       <c r="D74" t="n">
         <v>-0.9833</v>
@@ -3857,7 +3857,7 @@
         <v>-1.4881</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.8999</v>
       </c>
       <c r="D75" t="n">
         <v>-1.0225</v>
@@ -3903,7 +3903,7 @@
         <v>-1.5723</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.9509</v>
       </c>
       <c r="D76" t="n">
         <v>-1.0565</v>
@@ -3949,7 +3949,7 @@
         <v>-1.6939</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.0244</v>
       </c>
       <c r="D77" t="n">
         <v>-1.1057</v>
@@ -3995,7 +3995,7 @@
         <v>-2</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.2095</v>
       </c>
       <c r="D78" t="n">
         <v>-1.2293</v>
@@ -4041,7 +4041,7 @@
         <v>-2.0026</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.2111</v>
       </c>
       <c r="D79" t="n">
         <v>-1.2304</v>
@@ -4087,7 +4087,7 @@
         <v>-2.3113</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.3978</v>
       </c>
       <c r="D80" t="n">
         <v>-1.3551</v>
@@ -4133,7 +4133,7 @@
         <v>-2.5779</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-1.559</v>
       </c>
       <c r="D81" t="n">
         <v>-1.4628</v>
@@ -4179,7 +4179,7 @@
         <v>-2.9508</v>
       </c>
       <c r="C82" t="n">
-        <v>-0</v>
+        <v>-1.7845</v>
       </c>
       <c r="D82" t="n">
         <v>-1.6134</v>

--- a/database/event/8041/event_8041_evp_summary.xlsx
+++ b/database/event/8041/event_8041_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.0577</v>
+        <v>11.0115</v>
       </c>
       <c r="C2" t="n">
-        <v>6.6872</v>
+        <v>6.6593</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0457</v>
+        <v>3.9431</v>
       </c>
       <c r="E2" t="n">
-        <v>11.0577</v>
+        <v>11.0115</v>
       </c>
       <c r="F2" t="n">
-        <v>5.6119</v>
+        <v>5.5657</v>
       </c>
       <c r="G2" t="n">
         <v>5.4459</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4963</v>
+        <v>6.4239</v>
       </c>
       <c r="I2" t="n">
         <v>6.5875</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.2835</v>
+        <v>8.269399999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>5.0095</v>
+        <v>5.001</v>
       </c>
       <c r="D3" t="n">
-        <v>2.925</v>
+        <v>2.8506</v>
       </c>
       <c r="E3" t="n">
-        <v>8.2835</v>
+        <v>8.269399999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7995</v>
+        <v>3.7853</v>
       </c>
       <c r="G3" t="n">
         <v>4.484</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7995</v>
+        <v>3.7853</v>
       </c>
       <c r="I3" t="n">
         <v>3.8172</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.757</v>
+        <v>7.7163</v>
       </c>
       <c r="C4" t="n">
-        <v>4.6911</v>
+        <v>4.6665</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7123</v>
+        <v>2.6303</v>
       </c>
       <c r="E4" t="n">
-        <v>7.757</v>
+        <v>7.7163</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6574</v>
+        <v>3.6166</v>
       </c>
       <c r="G4" t="n">
         <v>4.0996</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6574</v>
+        <v>3.6166</v>
       </c>
       <c r="I4" t="n">
         <v>3.7087</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.9378</v>
+        <v>6.9036</v>
       </c>
       <c r="C5" t="n">
-        <v>4.1957</v>
+        <v>4.175</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3814</v>
+        <v>2.3065</v>
       </c>
       <c r="E5" t="n">
-        <v>6.9378</v>
+        <v>6.9036</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5325</v>
+        <v>4.4984</v>
       </c>
       <c r="G5" t="n">
         <v>2.4053</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8039</v>
+        <v>4.7504</v>
       </c>
       <c r="I5" t="n">
         <v>4.8713</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.075</v>
+        <v>6.0623</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6739</v>
+        <v>3.6662</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0328</v>
+        <v>1.9713</v>
       </c>
       <c r="E6" t="n">
-        <v>6.075</v>
+        <v>6.0623</v>
       </c>
       <c r="F6" t="n">
-        <v>3.397</v>
+        <v>3.3843</v>
       </c>
       <c r="G6" t="n">
         <v>2.678</v>
       </c>
       <c r="H6" t="n">
-        <v>3.397</v>
+        <v>3.3843</v>
       </c>
       <c r="I6" t="n">
         <v>3.4128</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.3715</v>
+        <v>5.3652</v>
       </c>
       <c r="C7" t="n">
-        <v>3.2485</v>
+        <v>3.2446</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7486</v>
+        <v>1.6936</v>
       </c>
       <c r="E7" t="n">
-        <v>5.3715</v>
+        <v>5.3652</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6855</v>
+        <v>1.6792</v>
       </c>
       <c r="G7" t="n">
         <v>3.686</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6855</v>
+        <v>1.6792</v>
       </c>
       <c r="I7" t="n">
         <v>1.6934</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.3357</v>
+        <v>5.336</v>
       </c>
       <c r="C8" t="n">
-        <v>3.2268</v>
+        <v>3.227</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7341</v>
+        <v>1.682</v>
       </c>
       <c r="E8" t="n">
-        <v>5.3357</v>
+        <v>5.336</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0668</v>
+        <v>-0.0665</v>
       </c>
       <c r="G8" t="n">
         <v>5.4025</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0668</v>
+        <v>-0.0665</v>
       </c>
       <c r="I8" t="n">
         <v>-0.06710000000000001</v>
@@ -824,7 +824,7 @@
         <v>3.1126</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6579</v>
+        <v>1.6066</v>
       </c>
       <c r="E9" t="n">
         <v>5.1469</v>
@@ -870,7 +870,7 @@
         <v>3.0863</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6403</v>
+        <v>1.5892</v>
       </c>
       <c r="E10" t="n">
         <v>5.1033</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.0053</v>
+        <v>4.9921</v>
       </c>
       <c r="C11" t="n">
-        <v>3.027</v>
+        <v>3.019</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6007</v>
+        <v>1.5449</v>
       </c>
       <c r="E11" t="n">
-        <v>5.0053</v>
+        <v>4.9921</v>
       </c>
       <c r="F11" t="n">
-        <v>5.0053</v>
+        <v>4.9921</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5453</v>
+        <v>5.5246</v>
       </c>
       <c r="I11" t="n">
         <v>5.5711</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.5982</v>
+        <v>4.5971</v>
       </c>
       <c r="C12" t="n">
-        <v>2.7808</v>
+        <v>2.7801</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4362</v>
+        <v>1.3876</v>
       </c>
       <c r="E12" t="n">
-        <v>4.5982</v>
+        <v>4.5971</v>
       </c>
       <c r="F12" t="n">
-        <v>4.8828</v>
+        <v>3.7044</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2846</v>
+        <v>0.8927</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3532</v>
+        <v>3.7044</v>
       </c>
       <c r="I12" t="n">
-        <v>5.4031</v>
+        <v>3.0025</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2846</v>
+        <v>0.8927</v>
       </c>
       <c r="K12" t="n">
-        <v>249</v>
+        <v>185</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M12" t="n">
-        <v>5.1185</v>
+        <v>3.8952</v>
       </c>
       <c r="N12" t="n">
-        <v>290</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.5971</v>
+        <v>4.5728</v>
       </c>
       <c r="C13" t="n">
-        <v>2.7801</v>
+        <v>2.7654</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4358</v>
+        <v>1.3779</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5971</v>
+        <v>4.5728</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7044</v>
+        <v>4.8574</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8927</v>
+        <v>-0.2846</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7044</v>
+        <v>5.3133</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0025</v>
+        <v>5.4031</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8927</v>
+        <v>-0.2846</v>
       </c>
       <c r="K13" t="n">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="L13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8952</v>
+        <v>5.1185</v>
       </c>
       <c r="N13" t="n">
-        <v>227</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14">
@@ -1054,7 +1054,7 @@
         <v>2.6387</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3413</v>
+        <v>1.2944</v>
       </c>
       <c r="E14" t="n">
         <v>4.3633</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.0867</v>
+        <v>4.0769</v>
       </c>
       <c r="C15" t="n">
-        <v>2.4715</v>
+        <v>2.4655</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2296</v>
+        <v>1.1803</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0867</v>
+        <v>4.0769</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0867</v>
+        <v>4.0769</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1048</v>
+        <v>4.0895</v>
       </c>
       <c r="I15" t="n">
         <v>4.1239</v>
@@ -1146,7 +1146,7 @@
         <v>2.3315</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1361</v>
+        <v>1.092</v>
       </c>
       <c r="E16" t="n">
         <v>3.8553</v>
@@ -1192,7 +1192,7 @@
         <v>2.1636</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0239</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="E17" t="n">
         <v>3.5777</v>
@@ -1238,7 +1238,7 @@
         <v>2.0014</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9156</v>
+        <v>0.8746</v>
       </c>
       <c r="E18" t="n">
         <v>3.3095</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.9205</v>
+        <v>2.9001</v>
       </c>
       <c r="C19" t="n">
-        <v>1.7662</v>
+        <v>1.7539</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7585</v>
+        <v>0.7115</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9205</v>
+        <v>2.9001</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7443</v>
+        <v>2.7239</v>
       </c>
       <c r="G19" t="n">
         <v>0.1762</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7443</v>
+        <v>2.7239</v>
       </c>
       <c r="I19" t="n">
         <v>2.77</v>
@@ -1330,7 +1330,7 @@
         <v>1.675</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6975</v>
+        <v>0.6595</v>
       </c>
       <c r="E20" t="n">
         <v>2.7697</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2779</v>
+        <v>2.2535</v>
       </c>
       <c r="C21" t="n">
-        <v>1.3776</v>
+        <v>1.3628</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4989</v>
+        <v>0.4539</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2779</v>
+        <v>2.2535</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1882</v>
+        <v>2.1638</v>
       </c>
       <c r="G21" t="n">
         <v>0.0897</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1882</v>
+        <v>2.1638</v>
       </c>
       <c r="I21" t="n">
         <v>2.2188</v>
@@ -1422,7 +1422,7 @@
         <v>1.3126</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4555</v>
+        <v>0.4208</v>
       </c>
       <c r="E22" t="n">
         <v>2.1705</v>
@@ -1468,7 +1468,7 @@
         <v>1.297</v>
       </c>
       <c r="D23" t="n">
-        <v>0.445</v>
+        <v>0.4105</v>
       </c>
       <c r="E23" t="n">
         <v>2.1447</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.1376</v>
+        <v>2.1183</v>
       </c>
       <c r="C24" t="n">
-        <v>1.2927</v>
+        <v>1.2811</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4422</v>
+        <v>0.4</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1376</v>
+        <v>2.1183</v>
       </c>
       <c r="F24" t="n">
-        <v>2.595</v>
+        <v>2.5757</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4574</v>
       </c>
       <c r="H24" t="n">
-        <v>2.595</v>
+        <v>2.5757</v>
       </c>
       <c r="I24" t="n">
         <v>2.6193</v>
@@ -1560,7 +1560,7 @@
         <v>1.2495</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4133</v>
+        <v>0.3792</v>
       </c>
       <c r="E25" t="n">
         <v>2.0661</v>
@@ -1606,7 +1606,7 @@
         <v>1.2307</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4008</v>
+        <v>0.3669</v>
       </c>
       <c r="E26" t="n">
         <v>2.0351</v>
@@ -1652,7 +1652,7 @@
         <v>1.0847</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3032</v>
+        <v>0.2707</v>
       </c>
       <c r="E27" t="n">
         <v>1.7936</v>
@@ -1698,7 +1698,7 @@
         <v>1.0552</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2835</v>
+        <v>0.2513</v>
       </c>
       <c r="E28" t="n">
         <v>1.7449</v>
@@ -1744,7 +1744,7 @@
         <v>0.9918</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2412</v>
+        <v>0.2095</v>
       </c>
       <c r="E29" t="n">
         <v>1.64</v>
@@ -1790,7 +1790,7 @@
         <v>0.9623</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2215</v>
+        <v>0.1901</v>
       </c>
       <c r="E30" t="n">
         <v>1.5913</v>
@@ -1836,7 +1836,7 @@
         <v>0.7995</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1127</v>
+        <v>0.0828</v>
       </c>
       <c r="E31" t="n">
         <v>1.322</v>
@@ -1882,7 +1882,7 @@
         <v>0.6882</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0384</v>
+        <v>0.0095</v>
       </c>
       <c r="E32" t="n">
         <v>1.138</v>
@@ -1928,7 +1928,7 @@
         <v>0.678</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0315</v>
+        <v>0.0027</v>
       </c>
       <c r="E33" t="n">
         <v>1.1211</v>
@@ -1974,7 +1974,7 @@
         <v>0.4775</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1024</v>
+        <v>-0.1293</v>
       </c>
       <c r="E34" t="n">
         <v>0.7896</v>
@@ -2020,7 +2020,7 @@
         <v>0.4742</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1046</v>
+        <v>-0.1315</v>
       </c>
       <c r="E35" t="n">
         <v>0.7841</v>
@@ -2066,7 +2066,7 @@
         <v>0.437</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1294</v>
+        <v>-0.156</v>
       </c>
       <c r="E36" t="n">
         <v>0.7226</v>
@@ -2112,7 +2112,7 @@
         <v>0.4045</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1512</v>
+        <v>-0.1775</v>
       </c>
       <c r="E37" t="n">
         <v>0.6688</v>
@@ -2158,7 +2158,7 @@
         <v>0.3879</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1623</v>
+        <v>-0.1884</v>
       </c>
       <c r="E38" t="n">
         <v>0.6414</v>
@@ -2204,7 +2204,7 @@
         <v>0.3578</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1823</v>
+        <v>-0.2082</v>
       </c>
       <c r="E39" t="n">
         <v>0.5917</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5578</v>
+        <v>0.5501</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3373</v>
+        <v>0.3327</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.196</v>
+        <v>-0.2248</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5578</v>
+        <v>0.5501</v>
       </c>
       <c r="F40" t="n">
-        <v>1.0375</v>
+        <v>1.0298</v>
       </c>
       <c r="G40" t="n">
         <v>-0.4797</v>
       </c>
       <c r="H40" t="n">
-        <v>1.0375</v>
+        <v>1.0298</v>
       </c>
       <c r="I40" t="n">
         <v>1.0472</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5507</v>
+        <v>0.5487</v>
       </c>
       <c r="C41" t="n">
-        <v>0.333</v>
+        <v>0.3318</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1989</v>
+        <v>-0.2253</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5507</v>
+        <v>0.5487</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5507</v>
+        <v>0.5487</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5507</v>
+        <v>0.5487</v>
       </c>
       <c r="I41" t="n">
         <v>0.5533</v>
@@ -2342,7 +2342,7 @@
         <v>0.3154</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2107</v>
+        <v>-0.2361</v>
       </c>
       <c r="E42" t="n">
         <v>0.5215</v>
@@ -2388,7 +2388,7 @@
         <v>0.2911</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2269</v>
+        <v>-0.2522</v>
       </c>
       <c r="E43" t="n">
         <v>0.4813</v>
@@ -2434,7 +2434,7 @@
         <v>0.2487</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2552</v>
+        <v>-0.2801</v>
       </c>
       <c r="E44" t="n">
         <v>0.4112</v>
@@ -2480,7 +2480,7 @@
         <v>0.1285</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3355</v>
+        <v>-0.3593</v>
       </c>
       <c r="E45" t="n">
         <v>0.2125</v>
@@ -2526,7 +2526,7 @@
         <v>0.1153</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3444</v>
+        <v>-0.368</v>
       </c>
       <c r="E46" t="n">
         <v>0.1906</v>
@@ -2572,7 +2572,7 @@
         <v>0.1117</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3467</v>
+        <v>-0.3703</v>
       </c>
       <c r="E47" t="n">
         <v>0.1847</v>
@@ -2618,7 +2618,7 @@
         <v>0.0997</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3548</v>
+        <v>-0.3783</v>
       </c>
       <c r="E48" t="n">
         <v>0.1648</v>
@@ -2664,7 +2664,7 @@
         <v>0.076</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3706</v>
+        <v>-0.3938</v>
       </c>
       <c r="E49" t="n">
         <v>0.1257</v>
@@ -2710,7 +2710,7 @@
         <v>0.0682</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3758</v>
+        <v>-0.399</v>
       </c>
       <c r="E50" t="n">
         <v>0.1127</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0301</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4414</v>
+        <v>-0.4637</v>
       </c>
       <c r="E51" t="n">
         <v>-0.0497</v>
@@ -2802,7 +2802,7 @@
         <v>-0.078</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4735</v>
+        <v>-0.4953</v>
       </c>
       <c r="E52" t="n">
         <v>-0.129</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1731</v>
+        <v>-0.1761</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1047</v>
+        <v>-0.1065</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4913</v>
+        <v>-0.5141</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1731</v>
+        <v>-0.1761</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4022</v>
+        <v>0.3992</v>
       </c>
       <c r="G53" t="n">
         <v>-0.5753</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4022</v>
+        <v>0.3992</v>
       </c>
       <c r="I53" t="n">
         <v>0.406</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1428</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5167</v>
+        <v>-0.538</v>
       </c>
       <c r="E54" t="n">
         <v>-0.2361</v>
@@ -2940,7 +2940,7 @@
         <v>-0.1756</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5387</v>
+        <v>-0.5596</v>
       </c>
       <c r="E55" t="n">
         <v>-0.2904</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1799</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5415</v>
+        <v>-0.5624</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2975</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1832</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5438</v>
+        <v>-0.5646</v>
       </c>
       <c r="E57" t="n">
         <v>-0.303</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2161</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5657</v>
+        <v>-0.5863</v>
       </c>
       <c r="E58" t="n">
         <v>-0.3574</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2276</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5734</v>
+        <v>-0.5939</v>
       </c>
       <c r="E59" t="n">
         <v>-0.3764</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2398</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5816</v>
+        <v>-0.6019</v>
       </c>
       <c r="E60" t="n">
         <v>-0.3966</v>
@@ -3216,7 +3216,7 @@
         <v>-0.2499</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5883</v>
+        <v>-0.6085</v>
       </c>
       <c r="E61" t="n">
         <v>-0.4132</v>
@@ -3262,7 +3262,7 @@
         <v>-0.271</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6024</v>
+        <v>-0.6224</v>
       </c>
       <c r="E62" t="n">
         <v>-0.4481</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2745</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6047</v>
+        <v>-0.6247</v>
       </c>
       <c r="E63" t="n">
         <v>-0.4539</v>
@@ -3354,7 +3354,7 @@
         <v>-0.288</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6137</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="E64" t="n">
         <v>-0.4762</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3224</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6367</v>
+        <v>-0.6563</v>
       </c>
       <c r="E65" t="n">
         <v>-0.5331</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4456</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.719</v>
+        <v>-0.7375</v>
       </c>
       <c r="E66" t="n">
         <v>-0.7368</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5414</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.783</v>
+        <v>-0.8006</v>
       </c>
       <c r="E67" t="n">
         <v>-0.8952</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.9054</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5484</v>
+        <v>-0.5475</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7877</v>
+        <v>-0.8046</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.9054</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.1188</v>
+        <v>-0.1174</v>
       </c>
       <c r="G68" t="n">
         <v>-0.788</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.1188</v>
+        <v>-0.1174</v>
       </c>
       <c r="I68" t="n">
         <v>-0.1204</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5534</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.791</v>
+        <v>-0.8084</v>
       </c>
       <c r="E69" t="n">
         <v>-0.915</v>
@@ -3630,7 +3630,7 @@
         <v>-0.5688</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8013</v>
+        <v>-0.8186</v>
       </c>
       <c r="E70" t="n">
         <v>-0.9406</v>
@@ -3676,7 +3676,7 @@
         <v>-0.5722</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8036</v>
+        <v>-0.8209</v>
       </c>
       <c r="E71" t="n">
         <v>-0.9462</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6048</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E72" t="n">
         <v>-1</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6093</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8284</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="E73" t="n">
         <v>-1.0075</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8413</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9833</v>
+        <v>-0.9981</v>
       </c>
       <c r="E74" t="n">
         <v>-1.3911</v>
@@ -3860,7 +3860,7 @@
         <v>-0.8999</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0225</v>
+        <v>-1.0368</v>
       </c>
       <c r="E75" t="n">
         <v>-1.4881</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9509</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0565</v>
+        <v>-1.0703</v>
       </c>
       <c r="E76" t="n">
         <v>-1.5723</v>
@@ -3952,7 +3952,7 @@
         <v>-1.0244</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1057</v>
+        <v>-1.1188</v>
       </c>
       <c r="E77" t="n">
         <v>-1.6939</v>
@@ -3998,7 +3998,7 @@
         <v>-1.2095</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E78" t="n">
         <v>-2</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.0026</v>
+        <v>-2.0004</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.2111</v>
+        <v>-1.2098</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2304</v>
+        <v>-1.2409</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.0026</v>
+        <v>-2.0004</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.5981</v>
+        <v>-0.5959</v>
       </c>
       <c r="G79" t="n">
         <v>-1.4045</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.5981</v>
+        <v>-0.5959</v>
       </c>
       <c r="I79" t="n">
         <v>-0.6009</v>
@@ -4090,7 +4090,7 @@
         <v>-1.3978</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3551</v>
+        <v>-1.3647</v>
       </c>
       <c r="E80" t="n">
         <v>-2.3113</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.5779</v>
+        <v>-2.5683</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.559</v>
+        <v>-1.5532</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.4628</v>
+        <v>-1.4671</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.5779</v>
+        <v>-2.5683</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.5779</v>
+        <v>-2.5683</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.5779</v>
+        <v>-2.5683</v>
       </c>
       <c r="I81" t="n">
         <v>-2.5899</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-2.9508</v>
+        <v>-2.9398</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.7845</v>
+        <v>-1.7779</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.6134</v>
+        <v>-1.6151</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.9508</v>
+        <v>-2.9398</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.9508</v>
+        <v>-2.9398</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-2.9508</v>
+        <v>-2.9398</v>
       </c>
       <c r="I82" t="n">
         <v>-2.9645</v>

--- a/database/event/8041/event_8041_evp_summary.xlsx
+++ b/database/event/8041/event_8041_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.126099999999999</v>
+        <v>9.321999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>5.5191</v>
+        <v>5.6375</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5302</v>
+        <v>3.5501</v>
       </c>
       <c r="E2" t="n">
-        <v>9.126099999999999</v>
+        <v>9.321999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2471</v>
+        <v>4.2338</v>
       </c>
       <c r="G2" t="n">
-        <v>4.879</v>
+        <v>4.8674</v>
       </c>
       <c r="H2" t="n">
-        <v>6.5706</v>
+        <v>6.5415</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0918</v>
+        <v>7.0604</v>
       </c>
       <c r="J2" t="n">
-        <v>4.879</v>
+        <v>4.8674</v>
       </c>
       <c r="K2" t="n">
         <v>215</v>
@@ -529,7 +529,7 @@
         <v>217</v>
       </c>
       <c r="M2" t="n">
-        <v>11.9708</v>
+        <v>11.9278</v>
       </c>
       <c r="N2" t="n">
         <v>432</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.3819</v>
+        <v>7.6467</v>
       </c>
       <c r="C3" t="n">
-        <v>4.4643</v>
+        <v>4.6244</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7362</v>
+        <v>2.8018</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3819</v>
+        <v>7.6467</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4508</v>
+        <v>3.4467</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9311</v>
+        <v>3.9317</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8277</v>
+        <v>4.8188</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9521</v>
+        <v>4.943</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9311</v>
+        <v>3.9317</v>
       </c>
       <c r="K3" t="n">
         <v>153</v>
@@ -575,7 +575,7 @@
         <v>154</v>
       </c>
       <c r="M3" t="n">
-        <v>8.883199999999999</v>
+        <v>8.874700000000001</v>
       </c>
       <c r="N3" t="n">
         <v>307</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.3651</v>
+        <v>7.463</v>
       </c>
       <c r="C4" t="n">
-        <v>4.4541</v>
+        <v>4.5133</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7285</v>
+        <v>2.7197</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3651</v>
+        <v>7.463</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4052</v>
+        <v>3.3937</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9599</v>
+        <v>3.9595</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7281</v>
+        <v>4.7028</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1031</v>
+        <v>5.0758</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9599</v>
+        <v>3.9595</v>
       </c>
       <c r="K4" t="n">
         <v>215</v>
@@ -621,7 +621,7 @@
         <v>217</v>
       </c>
       <c r="M4" t="n">
-        <v>9.063000000000001</v>
+        <v>9.035299999999999</v>
       </c>
       <c r="N4" t="n">
         <v>432</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.1427</v>
+        <v>6.3073</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7148</v>
+        <v>3.8144</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1721</v>
+        <v>2.2035</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1427</v>
+        <v>6.3073</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6592</v>
+        <v>3.6505</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4835</v>
+        <v>2.5033</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2839</v>
+        <v>5.2648</v>
       </c>
       <c r="I5" t="n">
-        <v>5.703</v>
+        <v>5.6824</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4835</v>
+        <v>2.5033</v>
       </c>
       <c r="K5" t="n">
         <v>215</v>
@@ -667,7 +667,7 @@
         <v>217</v>
       </c>
       <c r="M5" t="n">
-        <v>8.186500000000001</v>
+        <v>8.185700000000001</v>
       </c>
       <c r="N5" t="n">
         <v>432</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7428</v>
+        <v>5.9152</v>
       </c>
       <c r="C6" t="n">
-        <v>3.473</v>
+        <v>3.5773</v>
       </c>
       <c r="D6" t="n">
-        <v>1.99</v>
+        <v>2.0284</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7428</v>
+        <v>5.9152</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0802</v>
+        <v>2.1671</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6626</v>
+        <v>3.6836</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0802</v>
+        <v>2.1671</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1338</v>
+        <v>2.2229</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6626</v>
+        <v>3.6836</v>
       </c>
       <c r="K6" t="n">
         <v>153</v>
@@ -713,7 +713,7 @@
         <v>154</v>
       </c>
       <c r="M6" t="n">
-        <v>5.7964</v>
+        <v>5.9065</v>
       </c>
       <c r="N6" t="n">
         <v>307</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6352</v>
+        <v>5.717</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4079</v>
+        <v>3.4574</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9411</v>
+        <v>1.9398</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6352</v>
+        <v>5.717</v>
       </c>
       <c r="F7" t="n">
-        <v>2.892</v>
+        <v>2.8875</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7432</v>
+        <v>2.7134</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6047</v>
+        <v>3.5949</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6976</v>
+        <v>3.6875</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7432</v>
+        <v>2.7134</v>
       </c>
       <c r="K7" t="n">
         <v>153</v>
@@ -759,7 +759,7 @@
         <v>154</v>
       </c>
       <c r="M7" t="n">
-        <v>6.440799999999999</v>
+        <v>6.4009</v>
       </c>
       <c r="N7" t="n">
         <v>307</v>
@@ -768,231 +768,231 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.0801</v>
+        <v>5.244</v>
       </c>
       <c r="C8" t="n">
-        <v>3.0722</v>
+        <v>3.1713</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6884</v>
+        <v>1.7286</v>
       </c>
       <c r="E8" t="n">
-        <v>5.0801</v>
+        <v>5.244</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2657</v>
+        <v>4.5807</v>
       </c>
       <c r="G8" t="n">
-        <v>4.8144</v>
+        <v>0.4903</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2657</v>
+        <v>11.1481</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2725</v>
+        <v>6.0199</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8144</v>
+        <v>0.4903</v>
       </c>
       <c r="K8" t="n">
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="L8" t="n">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="M8" t="n">
-        <v>5.0869</v>
+        <v>6.5102</v>
       </c>
       <c r="N8" t="n">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.071</v>
+        <v>5.2229</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0667</v>
+        <v>3.1586</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6842</v>
+        <v>1.7191</v>
       </c>
       <c r="E9" t="n">
-        <v>5.071</v>
+        <v>5.2229</v>
       </c>
       <c r="F9" t="n">
         <v>4.5807</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4903</v>
+        <v>0.2654</v>
       </c>
       <c r="H9" t="n">
-        <v>11.1027</v>
+        <v>15.1541</v>
       </c>
       <c r="I9" t="n">
-        <v>5.9954</v>
+        <v>8.1831</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4903</v>
+        <v>0.2654</v>
       </c>
       <c r="K9" t="n">
-        <v>247</v>
+        <v>185</v>
       </c>
       <c r="L9" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="M9" t="n">
-        <v>6.4857</v>
+        <v>8.448499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>323</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.8468</v>
+        <v>5.013</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9311</v>
+        <v>3.0316</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5822</v>
+        <v>1.6254</v>
       </c>
       <c r="E10" t="n">
-        <v>4.8468</v>
+        <v>5.013</v>
       </c>
       <c r="F10" t="n">
-        <v>4.5807</v>
+        <v>0.1638</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2661</v>
+        <v>4.8015</v>
       </c>
       <c r="H10" t="n">
-        <v>15.1561</v>
+        <v>0.1638</v>
       </c>
       <c r="I10" t="n">
-        <v>8.184100000000001</v>
+        <v>0.168</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2661</v>
+        <v>4.8015</v>
       </c>
       <c r="K10" t="n">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="M10" t="n">
-        <v>8.450200000000001</v>
+        <v>4.9695</v>
       </c>
       <c r="N10" t="n">
-        <v>227</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.265</v>
+        <v>4.4901</v>
       </c>
       <c r="C11" t="n">
-        <v>2.5793</v>
+        <v>2.7154</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3173</v>
+        <v>1.3918</v>
       </c>
       <c r="E11" t="n">
-        <v>4.265</v>
+        <v>4.4901</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4028</v>
+        <v>4.1294</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8622</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.3328</v>
+        <v>6.3131</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4196</v>
+        <v>6.4758</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8622</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>185</v>
+        <v>238</v>
       </c>
       <c r="L11" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2818</v>
+        <v>6.4758</v>
       </c>
       <c r="N11" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.2242</v>
+        <v>4.4671</v>
       </c>
       <c r="C12" t="n">
-        <v>2.5546</v>
+        <v>2.7015</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2987</v>
+        <v>1.3815</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2242</v>
+        <v>4.4671</v>
       </c>
       <c r="F12" t="n">
-        <v>4.342</v>
+        <v>3.414</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1178</v>
+        <v>0.8619</v>
       </c>
       <c r="H12" t="n">
-        <v>9.4315</v>
+        <v>6.37</v>
       </c>
       <c r="I12" t="n">
-        <v>5.093</v>
+        <v>3.4398</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1178</v>
+        <v>0.8619</v>
       </c>
       <c r="K12" t="n">
-        <v>247</v>
+        <v>185</v>
       </c>
       <c r="L12" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="M12" t="n">
-        <v>4.9752</v>
+        <v>4.3017</v>
       </c>
       <c r="N12" t="n">
-        <v>323</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13">
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.1335</v>
+        <v>4.3825</v>
       </c>
       <c r="C13" t="n">
-        <v>2.4998</v>
+        <v>2.6503</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2575</v>
+        <v>1.3437</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1335</v>
+        <v>4.3825</v>
       </c>
       <c r="F13" t="n">
         <v>4.3839</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2504</v>
+        <v>-0.2507</v>
       </c>
       <c r="H13" t="n">
         <v>6.8701</v>
@@ -1026,7 +1026,7 @@
         <v>7.2287</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2504</v>
+        <v>-0.2507</v>
       </c>
       <c r="K13" t="n">
         <v>249</v>
@@ -1035,7 +1035,7 @@
         <v>41</v>
       </c>
       <c r="M13" t="n">
-        <v>6.9783</v>
+        <v>6.978</v>
       </c>
       <c r="N13" t="n">
         <v>290</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.1293</v>
+        <v>4.3384</v>
       </c>
       <c r="C14" t="n">
-        <v>2.4972</v>
+        <v>2.6237</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2555</v>
+        <v>1.324</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1293</v>
+        <v>4.3384</v>
       </c>
       <c r="F14" t="n">
-        <v>4.1293</v>
+        <v>4.3157</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.1178</v>
       </c>
       <c r="H14" t="n">
-        <v>6.3128</v>
+        <v>9.3451</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4755</v>
+        <v>5.0463</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.1178</v>
       </c>
       <c r="K14" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M14" t="n">
-        <v>6.4755</v>
+        <v>4.9285</v>
       </c>
       <c r="N14" t="n">
-        <v>238</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.5251</v>
+        <v>3.7359</v>
       </c>
       <c r="C15" t="n">
-        <v>2.1318</v>
+        <v>2.2593</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9805</v>
+        <v>1.0549</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5251</v>
+        <v>3.7359</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5251</v>
+        <v>3.5252</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9903</v>
+        <v>4.9906</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1189</v>
+        <v>5.1192</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.1189</v>
+        <v>5.1192</v>
       </c>
       <c r="N15" t="n">
         <v>238</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.4955</v>
+        <v>3.5182</v>
       </c>
       <c r="C16" t="n">
-        <v>2.1139</v>
+        <v>2.1277</v>
       </c>
       <c r="D16" t="n">
-        <v>0.967</v>
+        <v>0.9577</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4955</v>
+        <v>3.5182</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5343</v>
+        <v>3.5337</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0388</v>
+        <v>-0.039</v>
       </c>
       <c r="H16" t="n">
-        <v>6.7668</v>
+        <v>6.7647</v>
       </c>
       <c r="I16" t="n">
-        <v>3.654</v>
+        <v>3.6529</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0388</v>
+        <v>-0.039</v>
       </c>
       <c r="K16" t="n">
         <v>185</v>
@@ -1173,7 +1173,7 @@
         <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6152</v>
+        <v>3.6139</v>
       </c>
       <c r="N16" t="n">
         <v>227</v>
@@ -1182,633 +1182,633 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.326</v>
+        <v>3.3251</v>
       </c>
       <c r="C17" t="n">
-        <v>2.0114</v>
+        <v>2.0109</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8899</v>
+        <v>0.8714</v>
       </c>
       <c r="E17" t="n">
-        <v>3.326</v>
+        <v>3.3251</v>
       </c>
       <c r="F17" t="n">
-        <v>3.326</v>
+        <v>2.8718</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.4211</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5547</v>
+        <v>3.5606</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5547</v>
+        <v>3.7465</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.4211</v>
       </c>
       <c r="K17" t="n">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5547</v>
+        <v>4.1676</v>
       </c>
       <c r="N17" t="n">
-        <v>203</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.3034</v>
+        <v>3.3181</v>
       </c>
       <c r="C18" t="n">
-        <v>1.9978</v>
+        <v>2.0066</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8796</v>
+        <v>0.8683</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3034</v>
+        <v>3.3181</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0933</v>
+        <v>3.3258</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2101</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3118</v>
+        <v>4.5541</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8684</v>
+        <v>4.5541</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2101</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>247</v>
+        <v>203</v>
       </c>
       <c r="L18" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.0785</v>
+        <v>4.5541</v>
       </c>
       <c r="N18" t="n">
-        <v>323</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.2941</v>
+        <v>3.2981</v>
       </c>
       <c r="C19" t="n">
-        <v>1.9921</v>
+        <v>1.9945</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8753</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>3.2941</v>
+        <v>3.2981</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8718</v>
+        <v>3.1149</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4223</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5606</v>
+        <v>4.0927</v>
       </c>
       <c r="I19" t="n">
-        <v>3.7465</v>
+        <v>4.0927</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4223</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="L19" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1688</v>
+        <v>4.0927</v>
       </c>
       <c r="N19" t="n">
-        <v>290</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.1138</v>
+        <v>3.2876</v>
       </c>
       <c r="C20" t="n">
-        <v>1.8831</v>
+        <v>1.9882</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7933</v>
+        <v>0.8547</v>
       </c>
       <c r="E20" t="n">
-        <v>3.1138</v>
+        <v>3.2876</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1138</v>
+        <v>3.0845</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.2101</v>
       </c>
       <c r="H20" t="n">
-        <v>4.0901</v>
+        <v>5.2828</v>
       </c>
       <c r="I20" t="n">
-        <v>4.0901</v>
+        <v>2.8526</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.2101</v>
       </c>
       <c r="K20" t="n">
-        <v>203</v>
+        <v>247</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M20" t="n">
-        <v>4.0901</v>
+        <v>3.0627</v>
       </c>
       <c r="N20" t="n">
-        <v>203</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.7544</v>
+        <v>2.9643</v>
       </c>
       <c r="C21" t="n">
-        <v>1.6657</v>
+        <v>1.7927</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6297</v>
+        <v>0.7103</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7544</v>
+        <v>2.9643</v>
       </c>
       <c r="F21" t="n">
-        <v>2.8104</v>
+        <v>2.6375</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.056</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3783</v>
+        <v>3.0478</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3643</v>
+        <v>3.0478</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.056</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>247</v>
+        <v>157</v>
       </c>
       <c r="L21" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.3083</v>
+        <v>3.0478</v>
       </c>
       <c r="N21" t="n">
-        <v>323</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.6374</v>
+        <v>2.7181</v>
       </c>
       <c r="C22" t="n">
-        <v>1.595</v>
+        <v>1.6438</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5764</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6374</v>
+        <v>2.7181</v>
       </c>
       <c r="F22" t="n">
-        <v>2.6374</v>
+        <v>2.8107</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.056</v>
       </c>
       <c r="H22" t="n">
-        <v>3.0476</v>
+        <v>4.3795</v>
       </c>
       <c r="I22" t="n">
-        <v>3.0476</v>
+        <v>2.3649</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.056</v>
       </c>
       <c r="K22" t="n">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M22" t="n">
-        <v>3.0476</v>
+        <v>2.3089</v>
       </c>
       <c r="N22" t="n">
-        <v>157</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.5258</v>
+        <v>2.4431</v>
       </c>
       <c r="C23" t="n">
-        <v>1.5275</v>
+        <v>1.4775</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5256</v>
+        <v>0.4775</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5258</v>
+        <v>2.4431</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2703</v>
+        <v>2.4164</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2555</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2703</v>
+        <v>2.5639</v>
       </c>
       <c r="I23" t="n">
-        <v>2.4504</v>
+        <v>2.5639</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2555</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="L23" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.7059</v>
+        <v>2.5639</v>
       </c>
       <c r="N23" t="n">
-        <v>432</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.4163</v>
+        <v>2.3799</v>
       </c>
       <c r="C24" t="n">
-        <v>1.4613</v>
+        <v>1.4393</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4757</v>
+        <v>0.4492</v>
       </c>
       <c r="E24" t="n">
-        <v>2.4163</v>
+        <v>2.3799</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4163</v>
+        <v>2.2813</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.2553</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5635</v>
+        <v>2.2813</v>
       </c>
       <c r="I24" t="n">
-        <v>2.5635</v>
+        <v>2.4622</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.2553</v>
       </c>
       <c r="K24" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="M24" t="n">
-        <v>2.5635</v>
+        <v>2.7175</v>
       </c>
       <c r="N24" t="n">
-        <v>203</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>controlez</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.2141</v>
+        <v>2.2021</v>
       </c>
       <c r="C25" t="n">
-        <v>1.339</v>
+        <v>1.3317</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3837</v>
+        <v>0.3698</v>
       </c>
       <c r="E25" t="n">
-        <v>2.2141</v>
+        <v>2.2021</v>
       </c>
       <c r="F25" t="n">
-        <v>2.908</v>
+        <v>2.5097</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6939</v>
+        <v>-0.3502</v>
       </c>
       <c r="H25" t="n">
-        <v>4.7005</v>
+        <v>2.7681</v>
       </c>
       <c r="I25" t="n">
-        <v>2.5382</v>
+        <v>2.9126</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6939</v>
+        <v>-0.3502</v>
       </c>
       <c r="K25" t="n">
-        <v>185</v>
+        <v>249</v>
       </c>
       <c r="L25" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8443</v>
+        <v>2.5624</v>
       </c>
       <c r="N25" t="n">
-        <v>227</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>controlez</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.1599</v>
+        <v>2.079</v>
       </c>
       <c r="C26" t="n">
-        <v>1.3062</v>
+        <v>1.2573</v>
       </c>
       <c r="D26" t="n">
-        <v>0.359</v>
+        <v>0.3148</v>
       </c>
       <c r="E26" t="n">
-        <v>2.1599</v>
+        <v>2.079</v>
       </c>
       <c r="F26" t="n">
-        <v>2.5097</v>
+        <v>2.9238</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3498</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>2.7681</v>
+        <v>4.7525</v>
       </c>
       <c r="I26" t="n">
-        <v>2.9126</v>
+        <v>2.5663</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3498</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>249</v>
+        <v>185</v>
       </c>
       <c r="L26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M26" t="n">
-        <v>2.5628</v>
+        <v>1.8813</v>
       </c>
       <c r="N26" t="n">
-        <v>290</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alkaren</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.986</v>
+        <v>2.0424</v>
       </c>
       <c r="C27" t="n">
-        <v>1.201</v>
+        <v>1.2352</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2799</v>
+        <v>0.2985</v>
       </c>
       <c r="E27" t="n">
-        <v>1.986</v>
+        <v>2.0424</v>
       </c>
       <c r="F27" t="n">
-        <v>1.986</v>
+        <v>1.8928</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.986</v>
+        <v>1.8928</v>
       </c>
       <c r="I27" t="n">
-        <v>1.986</v>
+        <v>1.8928</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.986</v>
+        <v>1.8928</v>
       </c>
       <c r="N27" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.9673</v>
+        <v>2.0091</v>
       </c>
       <c r="C28" t="n">
-        <v>1.1897</v>
+        <v>1.215</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2714</v>
+        <v>0.2836</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9673</v>
+        <v>2.0091</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2733</v>
+        <v>1.67</v>
       </c>
       <c r="G28" t="n">
-        <v>0.694</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2733</v>
+        <v>1.67</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2733</v>
+        <v>1.67</v>
       </c>
       <c r="J28" t="n">
-        <v>0.694</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="L28" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.9673</v>
+        <v>1.67</v>
       </c>
       <c r="N28" t="n">
-        <v>234</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9402</v>
+        <v>1.9607</v>
       </c>
       <c r="C29" t="n">
-        <v>1.1733</v>
+        <v>1.1857</v>
       </c>
       <c r="D29" t="n">
-        <v>0.259</v>
+        <v>0.262</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9402</v>
+        <v>1.9607</v>
       </c>
       <c r="F29" t="n">
-        <v>2.477</v>
+        <v>2.2652</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.3562</v>
       </c>
       <c r="H29" t="n">
-        <v>3.2784</v>
+        <v>2.2652</v>
       </c>
       <c r="I29" t="n">
-        <v>1.7703</v>
+        <v>2.2652</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.3562</v>
       </c>
       <c r="K29" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L29" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2335</v>
+        <v>1.909</v>
       </c>
       <c r="N29" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.919</v>
+        <v>1.9554</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1605</v>
+        <v>1.1825</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2494</v>
+        <v>0.2596</v>
       </c>
       <c r="E30" t="n">
-        <v>1.919</v>
+        <v>1.9554</v>
       </c>
       <c r="F30" t="n">
-        <v>2.2754</v>
+        <v>1.2735</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3564</v>
+        <v>0.6854</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2754</v>
+        <v>1.2735</v>
       </c>
       <c r="I30" t="n">
-        <v>2.2754</v>
+        <v>1.2735</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3564</v>
+        <v>0.6854</v>
       </c>
       <c r="K30" t="n">
         <v>164</v>
@@ -1817,7 +1817,7 @@
         <v>70</v>
       </c>
       <c r="M30" t="n">
-        <v>1.919</v>
+        <v>1.9589</v>
       </c>
       <c r="N30" t="n">
         <v>234</v>
@@ -1826,47 +1826,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Alkaren</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.8849</v>
+        <v>1.9489</v>
       </c>
       <c r="C31" t="n">
-        <v>1.1399</v>
+        <v>1.1786</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2338</v>
+        <v>0.2567</v>
       </c>
       <c r="E31" t="n">
-        <v>1.8849</v>
+        <v>1.9489</v>
       </c>
       <c r="F31" t="n">
-        <v>1.8849</v>
+        <v>2.0056</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.8849</v>
+        <v>2.0056</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8849</v>
+        <v>2.0056</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.8849</v>
+        <v>2.0056</v>
       </c>
       <c r="N31" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.7517</v>
+        <v>1.8319</v>
       </c>
       <c r="C32" t="n">
-        <v>1.0594</v>
+        <v>1.1079</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1732</v>
+        <v>0.2044</v>
       </c>
       <c r="E32" t="n">
-        <v>1.7517</v>
+        <v>1.8319</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7517</v>
+        <v>1.7619</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7517</v>
+        <v>1.7619</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7517</v>
+        <v>1.7619</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.7517</v>
+        <v>1.7619</v>
       </c>
       <c r="N32" t="n">
         <v>194</v>
@@ -1918,139 +1918,139 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.6576</v>
+        <v>1.7094</v>
       </c>
       <c r="C33" t="n">
-        <v>1.0024</v>
+        <v>1.0338</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1304</v>
+        <v>0.1497</v>
       </c>
       <c r="E33" t="n">
-        <v>1.6576</v>
+        <v>1.7094</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6576</v>
+        <v>2.4867</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.537</v>
       </c>
       <c r="H33" t="n">
-        <v>1.6576</v>
+        <v>3.3105</v>
       </c>
       <c r="I33" t="n">
-        <v>1.6576</v>
+        <v>1.7876</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.537</v>
       </c>
       <c r="K33" t="n">
-        <v>98</v>
+        <v>185</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M33" t="n">
-        <v>1.6576</v>
+        <v>1.2506</v>
       </c>
       <c r="N33" t="n">
-        <v>98</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.3255</v>
+        <v>1.3727</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8016</v>
+        <v>0.8302</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0208</v>
+        <v>-0.0007</v>
       </c>
       <c r="E34" t="n">
-        <v>1.3255</v>
+        <v>1.3727</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3255</v>
+        <v>1.2783</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.3255</v>
+        <v>1.2783</v>
       </c>
       <c r="I34" t="n">
-        <v>1.3255</v>
+        <v>1.2783</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.3255</v>
+        <v>1.2783</v>
       </c>
       <c r="N34" t="n">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.2783</v>
+        <v>1.337</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7731</v>
+        <v>0.8086</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0423</v>
+        <v>-0.0166</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2783</v>
+        <v>1.337</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2783</v>
+        <v>1.3258</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2783</v>
+        <v>1.3258</v>
       </c>
       <c r="I35" t="n">
-        <v>1.2783</v>
+        <v>1.3258</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.2783</v>
+        <v>1.3258</v>
       </c>
       <c r="N35" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36">
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.2497</v>
+        <v>1.2383</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7558</v>
+        <v>0.7489</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0553</v>
+        <v>-0.0607</v>
       </c>
       <c r="E36" t="n">
-        <v>1.2497</v>
+        <v>1.2383</v>
       </c>
       <c r="F36" t="n">
         <v>1.4635</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.2138</v>
+        <v>-0.2059</v>
       </c>
       <c r="H36" t="n">
         <v>1.4635</v>
@@ -2084,7 +2084,7 @@
         <v>1.5399</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.2138</v>
+        <v>-0.2059</v>
       </c>
       <c r="K36" t="n">
         <v>249</v>
@@ -2093,7 +2093,7 @@
         <v>41</v>
       </c>
       <c r="M36" t="n">
-        <v>1.3261</v>
+        <v>1.334</v>
       </c>
       <c r="N36" t="n">
         <v>290</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.2255</v>
+        <v>1.1767</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7411</v>
+        <v>0.7116</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0663</v>
+        <v>-0.0882</v>
       </c>
       <c r="E37" t="n">
-        <v>1.2255</v>
+        <v>1.1767</v>
       </c>
       <c r="F37" t="n">
-        <v>1.2255</v>
+        <v>1.2259</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.2255</v>
+        <v>1.2259</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2571</v>
+        <v>1.2575</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.2571</v>
+        <v>1.2575</v>
       </c>
       <c r="N37" t="n">
         <v>238</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.1426</v>
+        <v>1.1719</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7087</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1041</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>1.1426</v>
+        <v>1.1719</v>
       </c>
       <c r="F38" t="n">
-        <v>1.1426</v>
+        <v>1.1416</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.1426</v>
+        <v>1.1416</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1426</v>
+        <v>1.1416</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1426</v>
+        <v>1.1416</v>
       </c>
       <c r="N38" t="n">
         <v>194</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.1217</v>
+        <v>1.1506</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6784</v>
+        <v>0.6958</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1136</v>
+        <v>-0.0999</v>
       </c>
       <c r="E39" t="n">
-        <v>1.1217</v>
+        <v>1.1506</v>
       </c>
       <c r="F39" t="n">
-        <v>1.1217</v>
+        <v>0.8378</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.1217</v>
+        <v>0.8378</v>
       </c>
       <c r="I39" t="n">
-        <v>1.1217</v>
+        <v>0.8378</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>195</v>
+        <v>141</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.1217</v>
+        <v>0.8378</v>
       </c>
       <c r="N39" t="n">
-        <v>195</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40">
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.0321</v>
+        <v>1.137</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6242</v>
+        <v>0.6876</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1544</v>
+        <v>-0.1059</v>
       </c>
       <c r="E40" t="n">
-        <v>1.0321</v>
+        <v>1.137</v>
       </c>
       <c r="F40" t="n">
         <v>1.0321</v>
@@ -2286,185 +2286,185 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9146</v>
+        <v>1.1032</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5531</v>
+        <v>0.6672</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2079</v>
+        <v>-0.121</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9146</v>
+        <v>1.1032</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9146</v>
+        <v>1.1211</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9146</v>
+        <v>1.1211</v>
       </c>
       <c r="I41" t="n">
-        <v>0.9146</v>
+        <v>1.1211</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>143</v>
+        <v>195</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.9146</v>
+        <v>1.1211</v>
       </c>
       <c r="N41" t="n">
-        <v>143</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8665</v>
+        <v>0.9163</v>
       </c>
       <c r="C42" t="n">
-        <v>0.524</v>
+        <v>0.5541</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2298</v>
+        <v>-0.2045</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8665</v>
+        <v>0.9163</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8665</v>
+        <v>0.9146</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8665</v>
+        <v>0.9146</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8665</v>
+        <v>0.9146</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.8665</v>
+        <v>0.9146</v>
       </c>
       <c r="N42" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7784</v>
+        <v>0.8798</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4707</v>
+        <v>0.5321</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2699</v>
+        <v>-0.2208</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7784</v>
+        <v>0.8798</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7784</v>
+        <v>0.6741</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7784</v>
+        <v>0.6741</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7784</v>
+        <v>0.6741</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.7784</v>
+        <v>0.6741</v>
       </c>
       <c r="N43" t="n">
-        <v>143</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7523</v>
+        <v>0.8339</v>
       </c>
       <c r="C44" t="n">
-        <v>0.455</v>
+        <v>0.5043</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2817</v>
+        <v>-0.2413</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7523</v>
+        <v>0.8339</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7523</v>
+        <v>0.7784</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7523</v>
+        <v>0.7784</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7523</v>
+        <v>0.7784</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7523</v>
+        <v>0.7784</v>
       </c>
       <c r="N44" t="n">
-        <v>203</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7377</v>
+        <v>0.7837</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4461</v>
+        <v>0.4739</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2884</v>
+        <v>-0.2638</v>
       </c>
       <c r="E45" t="n">
-        <v>0.7377</v>
+        <v>0.7837</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7377</v>
+        <v>0.7369</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7377</v>
+        <v>0.7369</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7377</v>
+        <v>0.7369</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.7377</v>
+        <v>0.7369</v>
       </c>
       <c r="N45" t="n">
         <v>195</v>
@@ -2516,461 +2516,461 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7248</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4383</v>
+        <v>0.3996</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2943</v>
+        <v>-0.3187</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7248</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>1.0283</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.3035</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.0283</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5553</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.3035</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>247</v>
+        <v>203</v>
       </c>
       <c r="L46" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2518</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>323</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6741</v>
+        <v>0.6437</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4077</v>
+        <v>0.3893</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3173</v>
+        <v>-0.3263</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6741</v>
+        <v>0.6437</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6741</v>
+        <v>1.01</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-0.3035</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6741</v>
+        <v>1.01</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6741</v>
+        <v>0.5454</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-0.3035</v>
       </c>
       <c r="K47" t="n">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6741</v>
+        <v>0.2419</v>
       </c>
       <c r="N47" t="n">
-        <v>80</v>
+        <v>323</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6542</v>
+        <v>0.595</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3956</v>
+        <v>0.3598</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3264</v>
+        <v>-0.348</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6542</v>
+        <v>0.595</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6542</v>
+        <v>0.4892</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6542</v>
+        <v>0.4892</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6542</v>
+        <v>0.4892</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6542</v>
+        <v>0.4892</v>
       </c>
       <c r="N48" t="n">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5693</v>
+        <v>0.5713</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3443</v>
+        <v>0.3455</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.365</v>
+        <v>-0.3586</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5693</v>
+        <v>0.5713</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.4352</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.3062</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.4352</v>
       </c>
       <c r="I49" t="n">
-        <v>0.9212</v>
+        <v>0.4352</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.3062</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>249</v>
+        <v>114</v>
       </c>
       <c r="L49" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.615</v>
+        <v>0.4352</v>
       </c>
       <c r="N49" t="n">
-        <v>290</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.552</v>
+        <v>0.5211</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3338</v>
+        <v>0.3151</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3729</v>
+        <v>-0.3811</v>
       </c>
       <c r="E50" t="n">
-        <v>0.552</v>
+        <v>0.5211</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6122</v>
+        <v>0.3378</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.0602</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6122</v>
+        <v>0.3378</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.3378</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.0602</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>215</v>
+        <v>98</v>
       </c>
       <c r="L50" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.6006</v>
+        <v>0.3378</v>
       </c>
       <c r="N50" t="n">
-        <v>432</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4892</v>
+        <v>0.5123</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2958</v>
+        <v>0.3098</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4015</v>
+        <v>-0.385</v>
       </c>
       <c r="E51" t="n">
-        <v>0.4892</v>
+        <v>0.5123</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4892</v>
+        <v>0.6545</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.4892</v>
+        <v>0.6545</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4892</v>
+        <v>0.6545</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.4892</v>
+        <v>0.6545</v>
       </c>
       <c r="N51" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4352</v>
+        <v>0.4237</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2632</v>
+        <v>0.2562</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4261</v>
+        <v>-0.4246</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4352</v>
+        <v>0.4237</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4352</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.2871</v>
       </c>
       <c r="H52" t="n">
-        <v>0.4352</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4352</v>
+        <v>0.9212</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.2871</v>
       </c>
       <c r="K52" t="n">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4352</v>
+        <v>0.6341</v>
       </c>
       <c r="N52" t="n">
-        <v>114</v>
+        <v>290</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3871</v>
+        <v>0.3655</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2341</v>
+        <v>0.221</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.448</v>
+        <v>-0.4506</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3871</v>
+        <v>0.3655</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3871</v>
+        <v>-0.347</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3871</v>
+        <v>-0.347</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3871</v>
+        <v>-0.347</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3871</v>
+        <v>0.1969000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>114</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.3379</v>
+        <v>0.3299</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2043</v>
+        <v>0.1995</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4704</v>
+        <v>-0.4665</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3379</v>
+        <v>0.3299</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3379</v>
+        <v>0.591</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>-0.0603</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3379</v>
+        <v>0.591</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3379</v>
+        <v>0.6379</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>-0.0603</v>
       </c>
       <c r="K54" t="n">
-        <v>98</v>
+        <v>215</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3379</v>
+        <v>0.5776</v>
       </c>
       <c r="N54" t="n">
-        <v>98</v>
+        <v>432</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2766</v>
+        <v>0.3196</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1673</v>
+        <v>0.1933</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4983</v>
+        <v>-0.4711</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2766</v>
+        <v>0.3196</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2766</v>
+        <v>0.3871</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2766</v>
+        <v>0.3871</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2766</v>
+        <v>0.3871</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2766</v>
+        <v>0.3871</v>
       </c>
       <c r="N55" t="n">
-        <v>157</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56">
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2388</v>
+        <v>0.2537</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1444</v>
+        <v>0.1534</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5155</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2388</v>
+        <v>0.2537</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2388</v>
+        <v>0.2587</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2388</v>
+        <v>0.2587</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2388</v>
+        <v>0.2587</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.2388</v>
+        <v>0.2587</v>
       </c>
       <c r="N56" t="n">
         <v>195</v>
@@ -3022,139 +3022,139 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2342</v>
+        <v>0.2049</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1416</v>
+        <v>0.1239</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.5223</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2342</v>
+        <v>0.2049</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8993</v>
+        <v>0.2674</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.6651</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8993</v>
+        <v>0.2674</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8993</v>
+        <v>0.2674</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.6651</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="L57" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2342</v>
+        <v>0.2674</v>
       </c>
       <c r="N57" t="n">
-        <v>234</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>xfl0ud</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2339</v>
+        <v>0.1613</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1415</v>
+        <v>0.0975</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5177</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2339</v>
+        <v>0.1613</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2339</v>
+        <v>0.011</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2339</v>
+        <v>0.011</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2339</v>
+        <v>0.011</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.2339</v>
+        <v>0.011</v>
       </c>
       <c r="N58" t="n">
-        <v>141</v>
+        <v>195</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.1965</v>
+        <v>0.1463</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1188</v>
+        <v>0.0885</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5485</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1965</v>
+        <v>0.1463</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3472</v>
+        <v>0.2769</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5437</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3472</v>
+        <v>0.2769</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3472</v>
+        <v>0.2769</v>
       </c>
       <c r="J59" t="n">
-        <v>0.5437</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="L59" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1965</v>
+        <v>0.2769</v>
       </c>
       <c r="N59" t="n">
-        <v>234</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60">
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.1582</v>
+        <v>0.1143</v>
       </c>
       <c r="C60" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5522</v>
+        <v>-0.5628</v>
       </c>
       <c r="E60" t="n">
-        <v>0.1582</v>
+        <v>0.1143</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1582</v>
+        <v>0.1814</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1582</v>
+        <v>0.1814</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1582</v>
+        <v>0.1814</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1582</v>
+        <v>0.1814</v>
       </c>
       <c r="N60" t="n">
         <v>194</v>
@@ -3206,81 +3206,81 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>xfl0ud</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0115</v>
+        <v>0.0799</v>
       </c>
       <c r="C61" t="n">
-        <v>0.007</v>
+        <v>0.0483</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.619</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0115</v>
+        <v>0.0799</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0115</v>
+        <v>-0.1744</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0115</v>
+        <v>-0.1744</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0115</v>
+        <v>-0.1744</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0115</v>
+        <v>-0.1744</v>
       </c>
       <c r="N61" t="n">
-        <v>195</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0034</v>
+        <v>0.0197</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0021</v>
+        <v>0.0119</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6227</v>
+        <v>-0.605</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0034</v>
+        <v>0.0197</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7285</v>
+        <v>0.8994</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.7251</v>
+        <v>-0.6649</v>
       </c>
       <c r="H62" t="n">
-        <v>0.7285</v>
+        <v>0.8994</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7285</v>
+        <v>0.8994</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.7251</v>
+        <v>-0.6649</v>
       </c>
       <c r="K62" t="n">
         <v>164</v>
@@ -3289,7 +3289,7 @@
         <v>70</v>
       </c>
       <c r="M62" t="n">
-        <v>0.00340000000000007</v>
+        <v>0.2344999999999999</v>
       </c>
       <c r="N62" t="n">
         <v>234</v>
@@ -3302,28 +3302,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.0089</v>
+        <v>0.0062</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.0054</v>
+        <v>0.0037</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6283</v>
+        <v>-0.6111</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.0089</v>
+        <v>0.0062</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.0089</v>
+        <v>-0.0274</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.0089</v>
+        <v>-0.0274</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0089</v>
+        <v>-0.0274</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.0089</v>
+        <v>-0.0274</v>
       </c>
       <c r="N63" t="n">
         <v>157</v>
@@ -3344,93 +3344,93 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.0834</v>
+        <v>-0.0145</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.0504</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6622</v>
+        <v>-0.6203</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.0834</v>
+        <v>-0.0145</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.0834</v>
+        <v>-0.0963</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.0834</v>
+        <v>-0.0963</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0834</v>
+        <v>-0.0963</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.0834</v>
+        <v>-0.0963</v>
       </c>
       <c r="N64" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.0963</v>
+        <v>-0.0585</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.0582</v>
+        <v>-0.0354</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.668</v>
+        <v>-0.64</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0963</v>
+        <v>-0.0585</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.0963</v>
+        <v>0.7291</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>-0.7249</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.0963</v>
+        <v>0.7291</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0963</v>
+        <v>0.7291</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>-0.7249</v>
       </c>
       <c r="K65" t="n">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.0963</v>
+        <v>0.004199999999999982</v>
       </c>
       <c r="N65" t="n">
-        <v>80</v>
+        <v>234</v>
       </c>
     </row>
     <row r="66">
@@ -3440,28 +3440,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.2942</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.0602</v>
+        <v>-0.1779</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6695</v>
+        <v>-0.7452</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.2942</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0997</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0997</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0997</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0997</v>
       </c>
       <c r="N66" t="n">
         <v>98</v>
@@ -3482,415 +3482,415 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.1744</v>
+        <v>-0.297</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1055</v>
+        <v>-0.1796</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7036</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.1744</v>
+        <v>-0.297</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.1744</v>
+        <v>-0.251</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.1744</v>
+        <v>-0.251</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1744</v>
+        <v>-0.251</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.1744</v>
+        <v>-0.251</v>
       </c>
       <c r="N67" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.2501</v>
+        <v>-0.3363</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.1512</v>
+        <v>-0.2034</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7381</v>
+        <v>-0.764</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.2501</v>
+        <v>-0.3363</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.2501</v>
+        <v>-0.0834</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.2501</v>
+        <v>-0.0834</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2501</v>
+        <v>-0.0834</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.2501</v>
+        <v>-0.0834</v>
       </c>
       <c r="N68" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.4447</v>
+        <v>-0.4476</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2689</v>
+        <v>-0.2707</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8266</v>
+        <v>-0.8138</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.4447</v>
+        <v>-0.4476</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.4447</v>
+        <v>-0.5082</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4447</v>
+        <v>-0.5082</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4447</v>
+        <v>-0.5082</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.4447</v>
+        <v>-0.5082</v>
       </c>
       <c r="N69" t="n">
-        <v>143</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.5082</v>
+        <v>-0.5512</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3073</v>
+        <v>-0.3333</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8555</v>
+        <v>-0.86</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.5082</v>
+        <v>-0.5512</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.5082</v>
+        <v>-0.6175</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.5082</v>
+        <v>-0.6175</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5082</v>
+        <v>-0.6175</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.5082</v>
+        <v>-0.6175</v>
       </c>
       <c r="N70" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.5878</v>
+        <v>-0.6776</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3555</v>
+        <v>-0.4098</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8918</v>
+        <v>-0.9165</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.5878</v>
+        <v>-0.6776</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.5878</v>
+        <v>-0.4447</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.5878</v>
+        <v>-0.4447</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5878</v>
+        <v>-0.4447</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.5878</v>
+        <v>-0.4447</v>
       </c>
       <c r="N71" t="n">
-        <v>80</v>
+        <v>143</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.601</v>
+        <v>-0.7014</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3635</v>
+        <v>-0.4242</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8978</v>
+        <v>-0.9271</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.601</v>
+        <v>-0.7014</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.601</v>
+        <v>-0.5878</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.601</v>
+        <v>-0.5878</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.601</v>
+        <v>-0.5878</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.601</v>
+        <v>-0.5878</v>
       </c>
       <c r="N72" t="n">
-        <v>141</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>sAw</t>
+          <t>C4LLM3SU3</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-1.2236</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4782</v>
+        <v>-0.74</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9842</v>
+        <v>-1.1604</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-1.2236</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.9974</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.9974</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.9974</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>41</v>
+        <v>141</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.9974</v>
       </c>
       <c r="N73" t="n">
-        <v>41</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C4LLM3SU3</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.0665</v>
+        <v>-1.2828</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.645</v>
+        <v>-0.7758</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1097</v>
+        <v>-1.1868</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0665</v>
+        <v>-1.2828</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.0665</v>
+        <v>-1.1552</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.0665</v>
+        <v>-1.1552</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.0665</v>
+        <v>-1.1552</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.0665</v>
+        <v>-1.1552</v>
       </c>
       <c r="N74" t="n">
-        <v>141</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>sAw</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.1555</v>
+        <v>-1.3998</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6988</v>
+        <v>-0.8465</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1502</v>
+        <v>-1.2391</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1555</v>
+        <v>-1.3998</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.1555</v>
+        <v>-0.791</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.1555</v>
+        <v>-0.791</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1555</v>
+        <v>-0.791</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.1555</v>
+        <v>-0.791</v>
       </c>
       <c r="N75" t="n">
-        <v>162</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76">
@@ -3900,16 +3900,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.3209</v>
+        <v>-1.5989</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7988</v>
+        <v>-0.9669</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2255</v>
+        <v>-1.328</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.3209</v>
+        <v>-1.5989</v>
       </c>
       <c r="F76" t="n">
         <v>-1.3209</v>
@@ -3942,185 +3942,185 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.4831</v>
+        <v>-1.806</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.8969</v>
+        <v>-1.0922</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2993</v>
+        <v>-1.4205</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.4831</v>
+        <v>-1.806</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.4831</v>
+        <v>-0.4091</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>-1.1992</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.4831</v>
+        <v>-0.4091</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.4831</v>
+        <v>-0.4196</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>-1.1992</v>
       </c>
       <c r="K77" t="n">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.4831</v>
+        <v>-1.6188</v>
       </c>
       <c r="N77" t="n">
-        <v>80</v>
+        <v>307</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.6345</v>
+        <v>-1.8655</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.9885</v>
+        <v>-1.1282</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3683</v>
+        <v>-1.4471</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.6345</v>
+        <v>-1.8655</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.4355</v>
+        <v>-1.6824</v>
       </c>
       <c r="G78" t="n">
-        <v>-1.199</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.4355</v>
+        <v>-1.6824</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.4467</v>
+        <v>-1.6824</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.199</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="L78" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.6457</v>
+        <v>-1.6824</v>
       </c>
       <c r="N78" t="n">
-        <v>307</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.681</v>
+        <v>-1.9661</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.0166</v>
+        <v>-1.189</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3894</v>
+        <v>-1.492</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.681</v>
+        <v>-1.9661</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.681</v>
+        <v>-1.8265</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.681</v>
+        <v>-1.8265</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.681</v>
+        <v>-1.8736</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>141</v>
+        <v>238</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.681</v>
+        <v>-1.8736</v>
       </c>
       <c r="N79" t="n">
-        <v>141</v>
+        <v>238</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.8007</v>
+        <v>-2.1862</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.089</v>
+        <v>-1.3221</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4439</v>
+        <v>-1.5903</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.8007</v>
+        <v>-2.1862</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.8007</v>
+        <v>-1.4831</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.8007</v>
+        <v>-1.4831</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.8471</v>
+        <v>-1.4831</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>238</v>
+        <v>80</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.8471</v>
+        <v>-1.4831</v>
       </c>
       <c r="N80" t="n">
-        <v>238</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81">
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.9355</v>
+        <v>-2.3736</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.1705</v>
+        <v>-1.4355</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5053</v>
+        <v>-1.6741</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.9355</v>
+        <v>-2.3736</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.9355</v>
+        <v>-1.9357</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.9355</v>
+        <v>-1.9357</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.9355</v>
+        <v>-1.9357</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.9355</v>
+        <v>-1.9357</v>
       </c>
       <c r="N81" t="n">
         <v>98</v>
@@ -4176,28 +4176,28 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-2.1453</v>
+        <v>-2.4198</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.2974</v>
+        <v>-1.4634</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.6008</v>
+        <v>-1.6947</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.1453</v>
+        <v>-2.4198</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.1453</v>
+        <v>-2.1449</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-2.1453</v>
+        <v>-2.1449</v>
       </c>
       <c r="I82" t="n">
-        <v>-2.2006</v>
+        <v>-2.2002</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>-2.2006</v>
+        <v>-2.2002</v>
       </c>
       <c r="N82" t="n">
         <v>238</v>
@@ -4912,13 +4912,13 @@
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8217</v>
+        <v>0.8413</v>
       </c>
       <c r="J17" t="n">
-        <v>18.8991</v>
+        <v>19.3499</v>
       </c>
     </row>
     <row r="18">
@@ -4955,10 +4955,10 @@
         <v>1.29</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7403</v>
+        <v>0.7399</v>
       </c>
       <c r="J18" t="n">
-        <v>17.0269</v>
+        <v>17.0177</v>
       </c>
     </row>
     <row r="19">
@@ -4995,10 +4995,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3669</v>
+        <v>0.3666</v>
       </c>
       <c r="J19" t="n">
-        <v>8.438700000000001</v>
+        <v>8.431800000000001</v>
       </c>
     </row>
     <row r="20">
@@ -5035,10 +5035,10 @@
         <v>1.1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3163</v>
+        <v>0.3159</v>
       </c>
       <c r="J20" t="n">
-        <v>7.2749</v>
+        <v>7.2657</v>
       </c>
     </row>
     <row r="21">
@@ -5075,10 +5075,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1647</v>
+        <v>-0.1651</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.7881</v>
+        <v>-3.7973</v>
       </c>
     </row>
     <row r="22">
@@ -5515,10 +5515,10 @@
         <v>1.18</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4392</v>
+        <v>0.4399</v>
       </c>
       <c r="J32" t="n">
-        <v>7.9056</v>
+        <v>7.9182</v>
       </c>
     </row>
     <row r="33">
@@ -5555,10 +5555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0883</v>
+        <v>-0.0881</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.5894</v>
+        <v>-1.5858</v>
       </c>
     </row>
     <row r="34">
@@ -5592,13 +5592,13 @@
         <v>18</v>
       </c>
       <c r="H34" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2588</v>
+        <v>-0.2682</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.6584</v>
+        <v>-4.8276</v>
       </c>
     </row>
     <row r="35">
@@ -5635,10 +5635,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3064</v>
+        <v>-0.3062</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.5152</v>
+        <v>-5.5116</v>
       </c>
     </row>
     <row r="36">
@@ -5675,10 +5675,10 @@
         <v>0.68</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3527</v>
+        <v>-0.3524</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.3486</v>
+        <v>-6.3432</v>
       </c>
     </row>
     <row r="37">
@@ -5715,10 +5715,10 @@
         <v>1.72</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3732</v>
+        <v>1.3723</v>
       </c>
       <c r="J37" t="n">
-        <v>24.7176</v>
+        <v>24.7014</v>
       </c>
     </row>
     <row r="38">
@@ -5755,10 +5755,10 @@
         <v>1.44</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9987</v>
+        <v>0.998</v>
       </c>
       <c r="J38" t="n">
-        <v>17.9766</v>
+        <v>17.964</v>
       </c>
     </row>
     <row r="39">
@@ -5792,13 +5792,13 @@
         <v>18</v>
       </c>
       <c r="H39" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9115</v>
+        <v>0.9472</v>
       </c>
       <c r="J39" t="n">
-        <v>16.407</v>
+        <v>17.0496</v>
       </c>
     </row>
     <row r="40">
@@ -5835,10 +5835,10 @@
         <v>1.18</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4888</v>
+        <v>0.4882</v>
       </c>
       <c r="J40" t="n">
-        <v>8.798400000000001</v>
+        <v>8.787599999999999</v>
       </c>
     </row>
     <row r="41">
@@ -5875,10 +5875,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7734</v>
+        <v>-0.774</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.9212</v>
+        <v>-13.932</v>
       </c>
     </row>
     <row r="42">
@@ -6315,10 +6315,10 @@
         <v>1.15</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3663</v>
+        <v>0.3657</v>
       </c>
       <c r="J52" t="n">
-        <v>6.9597</v>
+        <v>6.9483</v>
       </c>
     </row>
     <row r="53">
@@ -6355,10 +6355,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3288</v>
+        <v>0.3282</v>
       </c>
       <c r="J53" t="n">
-        <v>6.2472</v>
+        <v>6.2358</v>
       </c>
     </row>
     <row r="54">
@@ -6395,10 +6395,10 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0113</v>
+        <v>0.0109</v>
       </c>
       <c r="J54" t="n">
-        <v>0.2147</v>
+        <v>0.2071</v>
       </c>
     </row>
     <row r="55">
@@ -6432,13 +6432,13 @@
         <v>19</v>
       </c>
       <c r="H55" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3584</v>
+        <v>-0.3494</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.8096</v>
+        <v>-6.6386</v>
       </c>
     </row>
     <row r="56">
@@ -6475,10 +6475,10 @@
         <v>0.63</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4035</v>
+        <v>-0.4037</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.6665</v>
+        <v>-7.6703</v>
       </c>
     </row>
     <row r="57">
@@ -6715,10 +6715,10 @@
         <v>1.07</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2295</v>
+        <v>0.2288</v>
       </c>
       <c r="J62" t="n">
-        <v>4.131</v>
+        <v>4.1184</v>
       </c>
     </row>
     <row r="63">
@@ -6755,10 +6755,10 @@
         <v>0.97</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0434</v>
+        <v>-0.0437</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.7812</v>
+        <v>-0.7866</v>
       </c>
     </row>
     <row r="64">
@@ -6795,10 +6795,10 @@
         <v>0.88</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1568</v>
+        <v>-0.157</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.8224</v>
+        <v>-2.826</v>
       </c>
     </row>
     <row r="65">
@@ -6832,13 +6832,13 @@
         <v>18</v>
       </c>
       <c r="H65" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3776</v>
+        <v>-0.3687</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.7968</v>
+        <v>-6.6366</v>
       </c>
     </row>
     <row r="66">
@@ -6875,10 +6875,10 @@
         <v>0.63</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3956</v>
+        <v>-0.3958</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.1208</v>
+        <v>-7.1244</v>
       </c>
     </row>
     <row r="67">
@@ -6915,10 +6915,10 @@
         <v>2.35</v>
       </c>
       <c r="I67" t="n">
-        <v>1.9542</v>
+        <v>1.9549</v>
       </c>
       <c r="J67" t="n">
-        <v>35.1756</v>
+        <v>35.1882</v>
       </c>
     </row>
     <row r="68">
@@ -6955,10 +6955,10 @@
         <v>1.4</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7936</v>
+        <v>0.7938</v>
       </c>
       <c r="J68" t="n">
-        <v>14.2848</v>
+        <v>14.2884</v>
       </c>
     </row>
     <row r="69">
@@ -6995,10 +6995,10 @@
         <v>1.38</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7668</v>
+        <v>0.7669</v>
       </c>
       <c r="J69" t="n">
-        <v>13.8024</v>
+        <v>13.8042</v>
       </c>
     </row>
     <row r="70">
@@ -7032,13 +7032,13 @@
         <v>18</v>
       </c>
       <c r="H70" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1709</v>
+        <v>0.141</v>
       </c>
       <c r="J70" t="n">
-        <v>3.0762</v>
+        <v>2.538</v>
       </c>
     </row>
     <row r="71">
@@ -7075,10 +7075,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8901</v>
+        <v>-0.8899</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.0218</v>
+        <v>-16.0182</v>
       </c>
     </row>
     <row r="72">
@@ -8112,13 +8112,13 @@
         <v>24</v>
       </c>
       <c r="H97" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6783</v>
+        <v>0.6864</v>
       </c>
       <c r="J97" t="n">
-        <v>16.2792</v>
+        <v>16.4736</v>
       </c>
     </row>
     <row r="98">
@@ -8192,13 +8192,13 @@
         <v>24</v>
       </c>
       <c r="H99" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1138</v>
+        <v>-0.126</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.7312</v>
+        <v>-3.024</v>
       </c>
     </row>
     <row r="100">
@@ -8915,10 +8915,10 @@
         <v>1.59</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9387</v>
+        <v>0.9377</v>
       </c>
       <c r="J117" t="n">
-        <v>16.8966</v>
+        <v>16.8786</v>
       </c>
     </row>
     <row r="118">
@@ -8955,10 +8955,10 @@
         <v>0.85</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1877</v>
+        <v>-0.1879</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.3786</v>
+        <v>-3.3822</v>
       </c>
     </row>
     <row r="119">
@@ -8995,10 +8995,10 @@
         <v>0.84</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1978</v>
+        <v>-0.1979</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.5604</v>
+        <v>-3.5622</v>
       </c>
     </row>
     <row r="120">
@@ -9032,13 +9032,13 @@
         <v>18</v>
       </c>
       <c r="H120" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5431</v>
+        <v>-0.5347</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.7758</v>
+        <v>-9.624599999999999</v>
       </c>
     </row>
     <row r="121">
@@ -9075,10 +9075,10 @@
         <v>0.42</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.577</v>
+        <v>-0.5772</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.386</v>
+        <v>-10.3896</v>
       </c>
     </row>
     <row r="122">
@@ -9115,10 +9115,10 @@
         <v>1.63</v>
       </c>
       <c r="I122" t="n">
-        <v>1.12</v>
+        <v>1.1209</v>
       </c>
       <c r="J122" t="n">
-        <v>25.76</v>
+        <v>25.7807</v>
       </c>
     </row>
     <row r="123">
@@ -9152,13 +9152,13 @@
         <v>23</v>
       </c>
       <c r="H123" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0142</v>
+        <v>1.0016</v>
       </c>
       <c r="J123" t="n">
-        <v>23.3266</v>
+        <v>23.0368</v>
       </c>
     </row>
     <row r="124">
@@ -9195,10 +9195,10 @@
         <v>1.22</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5451</v>
+        <v>0.5455</v>
       </c>
       <c r="J124" t="n">
-        <v>12.5373</v>
+        <v>12.5465</v>
       </c>
     </row>
     <row r="125">
@@ -9235,10 +9235,10 @@
         <v>1.01</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0176</v>
+        <v>0.0183</v>
       </c>
       <c r="J125" t="n">
-        <v>0.4048</v>
+        <v>0.4209</v>
       </c>
     </row>
     <row r="126">
@@ -9272,13 +9272,13 @@
         <v>23</v>
       </c>
       <c r="H126" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.4154</v>
+        <v>-12.949</v>
       </c>
     </row>
     <row r="127">
@@ -9315,10 +9315,10 @@
         <v>1.13</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3293</v>
+        <v>0.3288</v>
       </c>
       <c r="J127" t="n">
-        <v>7.5739</v>
+        <v>7.5624</v>
       </c>
     </row>
     <row r="128">
@@ -9352,13 +9352,13 @@
         <v>23</v>
       </c>
       <c r="H128" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2708</v>
+        <v>0.2901</v>
       </c>
       <c r="J128" t="n">
-        <v>6.2284</v>
+        <v>6.6723</v>
       </c>
     </row>
     <row r="129">
@@ -9395,10 +9395,10 @@
         <v>0.97</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0526</v>
+        <v>-0.0528</v>
       </c>
       <c r="J129" t="n">
-        <v>-1.2098</v>
+        <v>-1.2144</v>
       </c>
     </row>
     <row r="130">
@@ -9435,10 +9435,10 @@
         <v>0.88</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1621</v>
+        <v>-0.1623</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.7283</v>
+        <v>-3.7329</v>
       </c>
     </row>
     <row r="131">
@@ -9475,10 +9475,10 @@
         <v>0.5</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5164</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.8772</v>
+        <v>-11.8818</v>
       </c>
     </row>
     <row r="132">
@@ -9912,13 +9912,13 @@
         <v>30</v>
       </c>
       <c r="H142" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3769</v>
+        <v>0.3894</v>
       </c>
       <c r="J142" t="n">
-        <v>11.307</v>
+        <v>11.682</v>
       </c>
     </row>
     <row r="143">
@@ -9955,10 +9955,10 @@
         <v>1.2</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3376</v>
+        <v>0.3372</v>
       </c>
       <c r="J143" t="n">
-        <v>10.128</v>
+        <v>10.116</v>
       </c>
     </row>
     <row r="144">
@@ -9995,10 +9995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1</v>
+        <v>-0.1001</v>
       </c>
       <c r="J144" t="n">
-        <v>-3</v>
+        <v>-3.003</v>
       </c>
     </row>
     <row r="145">
@@ -10035,10 +10035,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1593</v>
+        <v>-0.1594</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.779</v>
+        <v>-4.782</v>
       </c>
     </row>
     <row r="146">
@@ -10075,10 +10075,10 @@
         <v>0.8</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2535</v>
+        <v>-0.2537</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.605</v>
+        <v>-7.611</v>
       </c>
     </row>
     <row r="147">
@@ -10112,13 +10112,13 @@
         <v>30</v>
       </c>
       <c r="H147" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4616</v>
+        <v>0.453</v>
       </c>
       <c r="J147" t="n">
-        <v>13.848</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="148">
@@ -10155,10 +10155,10 @@
         <v>1.3</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4237</v>
+        <v>0.4239</v>
       </c>
       <c r="J148" t="n">
-        <v>12.711</v>
+        <v>12.717</v>
       </c>
     </row>
     <row r="149">
@@ -10195,10 +10195,10 @@
         <v>1.15</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2441</v>
+        <v>0.2443</v>
       </c>
       <c r="J149" t="n">
-        <v>7.323</v>
+        <v>7.329</v>
       </c>
     </row>
     <row r="150">
@@ -10235,10 +10235,10 @@
         <v>0.93</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1203</v>
+        <v>-0.1201</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.609</v>
+        <v>-3.603</v>
       </c>
     </row>
     <row r="151">
@@ -10275,10 +10275,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2516</v>
+        <v>-0.2514</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.548</v>
+        <v>-7.542</v>
       </c>
     </row>
     <row r="152">
@@ -12315,10 +12315,10 @@
         <v>1.14</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3493</v>
+        <v>0.3499</v>
       </c>
       <c r="J202" t="n">
-        <v>6.986</v>
+        <v>6.998</v>
       </c>
     </row>
     <row r="203">
@@ -12355,10 +12355,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0931</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.866</v>
+        <v>-1.862</v>
       </c>
     </row>
     <row r="204">
@@ -12395,10 +12395,10 @@
         <v>0.9</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1399</v>
+        <v>-0.1398</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.798</v>
+        <v>-2.796</v>
       </c>
     </row>
     <row r="205">
@@ -12432,13 +12432,13 @@
         <v>20</v>
       </c>
       <c r="H205" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1935</v>
+        <v>-0.2037</v>
       </c>
       <c r="J205" t="n">
-        <v>-3.87</v>
+        <v>-4.074</v>
       </c>
     </row>
     <row r="206">
@@ -12475,10 +12475,10 @@
         <v>0.73</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3115</v>
+        <v>-0.3113</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.23</v>
+        <v>-6.226</v>
       </c>
     </row>
     <row r="207">
@@ -12515,10 +12515,10 @@
         <v>1.97</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6822</v>
+        <v>1.6816</v>
       </c>
       <c r="J207" t="n">
-        <v>33.644</v>
+        <v>33.632</v>
       </c>
     </row>
     <row r="208">
@@ -12555,10 +12555,10 @@
         <v>1.27</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6804</v>
+        <v>0.6802</v>
       </c>
       <c r="J208" t="n">
-        <v>13.608</v>
+        <v>13.604</v>
       </c>
     </row>
     <row r="209">
@@ -12592,13 +12592,13 @@
         <v>20</v>
       </c>
       <c r="H209" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5979</v>
+        <v>0.6187</v>
       </c>
       <c r="J209" t="n">
-        <v>11.958</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="210">
@@ -12635,10 +12635,10 @@
         <v>1.12</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3458</v>
+        <v>0.3455</v>
       </c>
       <c r="J210" t="n">
-        <v>6.916</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="211">
@@ -12675,10 +12675,10 @@
         <v>0.89</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4224</v>
+        <v>-0.4227</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.448</v>
+        <v>-8.454000000000001</v>
       </c>
     </row>
     <row r="212">
@@ -13115,10 +13115,10 @@
         <v>2.08</v>
       </c>
       <c r="I222" t="n">
-        <v>1.1402</v>
+        <v>1.1412</v>
       </c>
       <c r="J222" t="n">
-        <v>27.3648</v>
+        <v>27.3888</v>
       </c>
     </row>
     <row r="223">
@@ -13152,13 +13152,13 @@
         <v>24</v>
       </c>
       <c r="H223" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7333</v>
       </c>
       <c r="J223" t="n">
-        <v>17.8176</v>
+        <v>17.5992</v>
       </c>
     </row>
     <row r="224">
@@ -13192,13 +13192,13 @@
         <v>24</v>
       </c>
       <c r="H224" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1939</v>
+        <v>-0.2044</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.6536</v>
+        <v>-4.9056</v>
       </c>
     </row>
     <row r="225">
@@ -13235,10 +13235,10 @@
         <v>0.76</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3048</v>
+        <v>-0.3045</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.3152</v>
+        <v>-7.308</v>
       </c>
     </row>
     <row r="226">
@@ -13275,10 +13275,10 @@
         <v>0.5</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5332</v>
+        <v>-0.533</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.7968</v>
+        <v>-12.792</v>
       </c>
     </row>
     <row r="227">
@@ -13712,13 +13712,13 @@
         <v>30</v>
       </c>
       <c r="H237" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="I237" t="n">
-        <v>0.7522</v>
+        <v>0.7313</v>
       </c>
       <c r="J237" t="n">
-        <v>22.566</v>
+        <v>21.939</v>
       </c>
     </row>
     <row r="238">
@@ -13755,10 +13755,10 @@
         <v>1.03</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1306</v>
+        <v>0.1308</v>
       </c>
       <c r="J238" t="n">
-        <v>3.918</v>
+        <v>3.924</v>
       </c>
     </row>
     <row r="239">
@@ -13795,10 +13795,10 @@
         <v>1.03</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1306</v>
+        <v>0.1308</v>
       </c>
       <c r="J239" t="n">
-        <v>3.918</v>
+        <v>3.924</v>
       </c>
     </row>
     <row r="240">
@@ -13835,10 +13835,10 @@
         <v>0.99</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0648</v>
+        <v>-0.0644</v>
       </c>
       <c r="J240" t="n">
-        <v>-1.944</v>
+        <v>-1.932</v>
       </c>
     </row>
     <row r="241">
@@ -13875,10 +13875,10 @@
         <v>0.87</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4275</v>
+        <v>-0.4271</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.825</v>
+        <v>-12.813</v>
       </c>
     </row>
     <row r="242">
@@ -13912,7 +13912,7 @@
         <v>17</v>
       </c>
       <c r="H242" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="I242" t="n">
         <v>1.9372</v>
@@ -13955,10 +13955,10 @@
         <v>1.43</v>
       </c>
       <c r="I243" t="n">
-        <v>0.962</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="J243" t="n">
-        <v>16.354</v>
+        <v>16.3574</v>
       </c>
     </row>
     <row r="244">
@@ -13995,10 +13995,10 @@
         <v>1.26</v>
       </c>
       <c r="I244" t="n">
-        <v>0.6361</v>
+        <v>0.6364</v>
       </c>
       <c r="J244" t="n">
-        <v>10.8137</v>
+        <v>10.8188</v>
       </c>
     </row>
     <row r="245">
@@ -14035,10 +14035,10 @@
         <v>1.18</v>
       </c>
       <c r="I245" t="n">
-        <v>0.4624</v>
+        <v>0.4626</v>
       </c>
       <c r="J245" t="n">
-        <v>7.8608</v>
+        <v>7.8642</v>
       </c>
     </row>
     <row r="246">
@@ -14075,10 +14075,10 @@
         <v>1.05</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1268</v>
+        <v>0.1271</v>
       </c>
       <c r="J246" t="n">
-        <v>2.1556</v>
+        <v>2.1607</v>
       </c>
     </row>
     <row r="247">
@@ -14115,10 +14115,10 @@
         <v>1.02</v>
       </c>
       <c r="I247" t="n">
-        <v>0.1518</v>
+        <v>0.1509</v>
       </c>
       <c r="J247" t="n">
-        <v>2.5806</v>
+        <v>2.5653</v>
       </c>
     </row>
     <row r="248">
@@ -14152,13 +14152,13 @@
         <v>17</v>
       </c>
       <c r="H248" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0347</v>
+        <v>-0.0198</v>
       </c>
       <c r="J248" t="n">
-        <v>-0.5899</v>
+        <v>-0.3366</v>
       </c>
     </row>
     <row r="249">
@@ -14195,10 +14195,10 @@
         <v>0.82</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2044</v>
+        <v>-0.2047</v>
       </c>
       <c r="J249" t="n">
-        <v>-3.4748</v>
+        <v>-3.4799</v>
       </c>
     </row>
     <row r="250">
@@ -14235,10 +14235,10 @@
         <v>0.42</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5656</v>
+        <v>-0.5658</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.6152</v>
+        <v>-9.618600000000001</v>
       </c>
     </row>
     <row r="251">
@@ -14275,10 +14275,10 @@
         <v>0.36</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6172</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.4924</v>
+        <v>-10.4958</v>
       </c>
     </row>
     <row r="252">
@@ -16915,10 +16915,10 @@
         <v>1.7</v>
       </c>
       <c r="I317" t="n">
-        <v>1.3487</v>
+        <v>1.3491</v>
       </c>
       <c r="J317" t="n">
-        <v>25.6253</v>
+        <v>25.6329</v>
       </c>
     </row>
     <row r="318">
@@ -16955,10 +16955,10 @@
         <v>1.44</v>
       </c>
       <c r="I318" t="n">
-        <v>0.9994</v>
+        <v>0.9997</v>
       </c>
       <c r="J318" t="n">
-        <v>18.9886</v>
+        <v>18.9943</v>
       </c>
     </row>
     <row r="319">
@@ -16995,10 +16995,10 @@
         <v>1.42</v>
       </c>
       <c r="I319" t="n">
-        <v>0.9661</v>
+        <v>0.9664</v>
       </c>
       <c r="J319" t="n">
-        <v>18.3559</v>
+        <v>18.3616</v>
       </c>
     </row>
     <row r="320">
@@ -17035,10 +17035,10 @@
         <v>0.98</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1502</v>
+        <v>-0.1498</v>
       </c>
       <c r="J320" t="n">
-        <v>-2.8538</v>
+        <v>-2.8462</v>
       </c>
     </row>
     <row r="321">
@@ -17072,13 +17072,13 @@
         <v>19</v>
       </c>
       <c r="H321" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3683</v>
+        <v>-0.3948</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.9977</v>
+        <v>-7.5012</v>
       </c>
     </row>
     <row r="322">
@@ -17115,10 +17115,10 @@
         <v>1.21</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3494</v>
+        <v>0.3497</v>
       </c>
       <c r="J322" t="n">
-        <v>12.5784</v>
+        <v>12.5892</v>
       </c>
     </row>
     <row r="323">
@@ -17155,10 +17155,10 @@
         <v>1.08</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1639</v>
+        <v>0.1641</v>
       </c>
       <c r="J323" t="n">
-        <v>5.9004</v>
+        <v>5.9076</v>
       </c>
     </row>
     <row r="324">
@@ -17195,10 +17195,10 @@
         <v>0.98</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.044</v>
+        <v>-0.0439</v>
       </c>
       <c r="J324" t="n">
-        <v>-1.584</v>
+        <v>-1.5804</v>
       </c>
     </row>
     <row r="325">
@@ -17232,13 +17232,13 @@
         <v>36</v>
       </c>
       <c r="H325" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1006</v>
+        <v>-0.113</v>
       </c>
       <c r="J325" t="n">
-        <v>-3.6216</v>
+        <v>-4.068</v>
       </c>
     </row>
     <row r="326">
@@ -17275,10 +17275,10 @@
         <v>0.89</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.16</v>
+        <v>-0.1598</v>
       </c>
       <c r="J326" t="n">
-        <v>-5.76</v>
+        <v>-5.7528</v>
       </c>
     </row>
     <row r="327">
@@ -18324,7 +18324,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -18915,10 +18915,10 @@
         <v>1.68</v>
       </c>
       <c r="I367" t="n">
-        <v>1.305</v>
+        <v>1.3046</v>
       </c>
       <c r="J367" t="n">
-        <v>23.49</v>
+        <v>23.4828</v>
       </c>
     </row>
     <row r="368">
@@ -18955,10 +18955,10 @@
         <v>1.39</v>
       </c>
       <c r="I368" t="n">
-        <v>0.8999</v>
+        <v>0.8998</v>
       </c>
       <c r="J368" t="n">
-        <v>16.1982</v>
+        <v>16.1964</v>
       </c>
     </row>
     <row r="369">
@@ -18995,10 +18995,10 @@
         <v>1.37</v>
       </c>
       <c r="I369" t="n">
-        <v>0.8639</v>
+        <v>0.8637</v>
       </c>
       <c r="J369" t="n">
-        <v>15.5502</v>
+        <v>15.5466</v>
       </c>
     </row>
     <row r="370">
@@ -19035,10 +19035,10 @@
         <v>1.3</v>
       </c>
       <c r="I370" t="n">
-        <v>0.7297</v>
+        <v>0.7295</v>
       </c>
       <c r="J370" t="n">
-        <v>13.1346</v>
+        <v>13.131</v>
       </c>
     </row>
     <row r="371">
@@ -19072,13 +19072,13 @@
         <v>18</v>
       </c>
       <c r="H371" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="I371" t="n">
-        <v>0.4525</v>
+        <v>0.4751</v>
       </c>
       <c r="J371" t="n">
-        <v>8.145</v>
+        <v>8.5518</v>
       </c>
     </row>
     <row r="372">
@@ -19315,10 +19315,10 @@
         <v>1.62</v>
       </c>
       <c r="I377" t="n">
-        <v>1.2297</v>
+        <v>1.23</v>
       </c>
       <c r="J377" t="n">
-        <v>23.3643</v>
+        <v>23.37</v>
       </c>
     </row>
     <row r="378">
@@ -19355,10 +19355,10 @@
         <v>1.54</v>
       </c>
       <c r="I378" t="n">
-        <v>1.1265</v>
+        <v>1.1268</v>
       </c>
       <c r="J378" t="n">
-        <v>21.4035</v>
+        <v>21.4092</v>
       </c>
     </row>
     <row r="379">
@@ -19395,10 +19395,10 @@
         <v>1.38</v>
       </c>
       <c r="I379" t="n">
-        <v>0.8822</v>
+        <v>0.8824</v>
       </c>
       <c r="J379" t="n">
-        <v>16.7618</v>
+        <v>16.7656</v>
       </c>
     </row>
     <row r="380">
@@ -19432,13 +19432,13 @@
         <v>19</v>
       </c>
       <c r="H380" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="I380" t="n">
-        <v>0.8457</v>
+        <v>0.8272</v>
       </c>
       <c r="J380" t="n">
-        <v>16.0683</v>
+        <v>15.7168</v>
       </c>
     </row>
     <row r="381">
@@ -19475,10 +19475,10 @@
         <v>0.99</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.1225</v>
+        <v>-0.1222</v>
       </c>
       <c r="J381" t="n">
-        <v>-2.3275</v>
+        <v>-2.3218</v>
       </c>
     </row>
     <row r="382">
@@ -20315,10 +20315,10 @@
         <v>1.22</v>
       </c>
       <c r="I402" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6169</v>
       </c>
       <c r="J402" t="n">
-        <v>17.9046</v>
+        <v>17.8901</v>
       </c>
     </row>
     <row r="403">
@@ -20355,10 +20355,10 @@
         <v>1.06</v>
       </c>
       <c r="I403" t="n">
-        <v>0.2218</v>
+        <v>0.2216</v>
       </c>
       <c r="J403" t="n">
-        <v>6.4322</v>
+        <v>6.4264</v>
       </c>
     </row>
     <row r="404">
@@ -20392,13 +20392,13 @@
         <v>29</v>
       </c>
       <c r="H404" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I404" t="n">
-        <v>0.1928</v>
+        <v>0.2216</v>
       </c>
       <c r="J404" t="n">
-        <v>5.5912</v>
+        <v>6.4264</v>
       </c>
     </row>
     <row r="405">
@@ -20435,10 +20435,10 @@
         <v>1.03</v>
       </c>
       <c r="I405" t="n">
-        <v>0.129</v>
+        <v>0.1288</v>
       </c>
       <c r="J405" t="n">
-        <v>3.741</v>
+        <v>3.7352</v>
       </c>
     </row>
     <row r="406">
@@ -20475,10 +20475,10 @@
         <v>0.9</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.3523</v>
+        <v>-0.3527</v>
       </c>
       <c r="J406" t="n">
-        <v>-10.2167</v>
+        <v>-10.2283</v>
       </c>
     </row>
     <row r="407">
@@ -22315,10 +22315,10 @@
         <v>1.63</v>
       </c>
       <c r="I452" t="n">
-        <v>1.2734</v>
+        <v>1.273</v>
       </c>
       <c r="J452" t="n">
-        <v>26.7414</v>
+        <v>26.733</v>
       </c>
     </row>
     <row r="453">
@@ -22355,10 +22355,10 @@
         <v>1.4</v>
       </c>
       <c r="I453" t="n">
-        <v>0.9434</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="J453" t="n">
-        <v>19.8114</v>
+        <v>19.803</v>
       </c>
     </row>
     <row r="454">
@@ -22392,13 +22392,13 @@
         <v>21</v>
       </c>
       <c r="H454" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="I454" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="J454" t="n">
-        <v>14.448</v>
+        <v>14.868</v>
       </c>
     </row>
     <row r="455">
@@ -22435,10 +22435,10 @@
         <v>1.11</v>
       </c>
       <c r="I455" t="n">
-        <v>0.3321</v>
+        <v>0.3318</v>
       </c>
       <c r="J455" t="n">
-        <v>6.9741</v>
+        <v>6.9678</v>
       </c>
     </row>
     <row r="456">
@@ -22475,10 +22475,10 @@
         <v>0.71</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.8274</v>
+        <v>-0.8277</v>
       </c>
       <c r="J456" t="n">
-        <v>-17.3754</v>
+        <v>-17.3817</v>
       </c>
     </row>
     <row r="457">
@@ -22712,13 +22712,13 @@
         <v>16</v>
       </c>
       <c r="H462" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="I462" t="n">
-        <v>1.7648</v>
+        <v>1.7546</v>
       </c>
       <c r="J462" t="n">
-        <v>28.2368</v>
+        <v>28.0736</v>
       </c>
     </row>
     <row r="463">
@@ -22752,13 +22752,13 @@
         <v>16</v>
       </c>
       <c r="H463" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I463" t="n">
-        <v>1.3754</v>
+        <v>1.3642</v>
       </c>
       <c r="J463" t="n">
-        <v>22.0064</v>
+        <v>21.8272</v>
       </c>
     </row>
     <row r="464">
@@ -22792,13 +22792,13 @@
         <v>16</v>
       </c>
       <c r="H464" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="I464" t="n">
-        <v>0.89</v>
+        <v>0.8721</v>
       </c>
       <c r="J464" t="n">
-        <v>14.24</v>
+        <v>13.9536</v>
       </c>
     </row>
     <row r="465">
@@ -22835,10 +22835,10 @@
         <v>1.17</v>
       </c>
       <c r="I465" t="n">
-        <v>0.438</v>
+        <v>0.4388</v>
       </c>
       <c r="J465" t="n">
-        <v>7.008</v>
+        <v>7.0208</v>
       </c>
     </row>
     <row r="466">
@@ -22875,10 +22875,10 @@
         <v>1.01</v>
       </c>
       <c r="I466" t="n">
-        <v>-0.0177</v>
+        <v>-0.0169</v>
       </c>
       <c r="J466" t="n">
-        <v>-0.2832</v>
+        <v>-0.2704</v>
       </c>
     </row>
     <row r="467">
@@ -22912,13 +22912,13 @@
         <v>16</v>
       </c>
       <c r="H467" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="I467" t="n">
-        <v>0.6186</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="J467" t="n">
-        <v>9.897600000000001</v>
+        <v>10.4112</v>
       </c>
     </row>
     <row r="468">
@@ -22955,10 +22955,10 @@
         <v>0.95</v>
       </c>
       <c r="I468" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0687</v>
       </c>
       <c r="J468" t="n">
-        <v>-1.0896</v>
+        <v>-1.0992</v>
       </c>
     </row>
     <row r="469">
@@ -22995,10 +22995,10 @@
         <v>0.88</v>
       </c>
       <c r="I469" t="n">
-        <v>-0.1537</v>
+        <v>-0.1542</v>
       </c>
       <c r="J469" t="n">
-        <v>-2.4592</v>
+        <v>-2.4672</v>
       </c>
     </row>
     <row r="470">
@@ -23035,10 +23035,10 @@
         <v>0.51</v>
       </c>
       <c r="I470" t="n">
-        <v>-0.4982</v>
+        <v>-0.4986</v>
       </c>
       <c r="J470" t="n">
-        <v>-7.9712</v>
+        <v>-7.9776</v>
       </c>
     </row>
     <row r="471">
@@ -23075,10 +23075,10 @@
         <v>0.45</v>
       </c>
       <c r="I471" t="n">
-        <v>-0.5497</v>
+        <v>-0.5501</v>
       </c>
       <c r="J471" t="n">
-        <v>-8.795199999999999</v>
+        <v>-8.801600000000001</v>
       </c>
     </row>
     <row r="472">
@@ -23112,13 +23112,13 @@
         <v>21</v>
       </c>
       <c r="H472" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="I472" t="n">
-        <v>0.5375</v>
+        <v>0.5606</v>
       </c>
       <c r="J472" t="n">
-        <v>11.2875</v>
+        <v>11.7726</v>
       </c>
     </row>
     <row r="473">
@@ -23155,10 +23155,10 @@
         <v>1.07</v>
       </c>
       <c r="I473" t="n">
-        <v>0.1548</v>
+        <v>0.1542</v>
       </c>
       <c r="J473" t="n">
-        <v>3.2508</v>
+        <v>3.2382</v>
       </c>
     </row>
     <row r="474">
@@ -23195,10 +23195,10 @@
         <v>0.87</v>
       </c>
       <c r="I474" t="n">
-        <v>-0.1772</v>
+        <v>-0.1775</v>
       </c>
       <c r="J474" t="n">
-        <v>-3.7212</v>
+        <v>-3.7275</v>
       </c>
     </row>
     <row r="475">
@@ -23235,10 +23235,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I475" t="n">
-        <v>-0.2393</v>
+        <v>-0.2397</v>
       </c>
       <c r="J475" t="n">
-        <v>-5.0253</v>
+        <v>-5.0337</v>
       </c>
     </row>
     <row r="476">
@@ -23275,10 +23275,10 @@
         <v>0.73</v>
       </c>
       <c r="I476" t="n">
-        <v>-0.3167</v>
+        <v>-0.3171</v>
       </c>
       <c r="J476" t="n">
-        <v>-6.6507</v>
+        <v>-6.6591</v>
       </c>
     </row>
     <row r="477">
@@ -23315,10 +23315,10 @@
         <v>1.96</v>
       </c>
       <c r="I477" t="n">
-        <v>1.043</v>
+        <v>1.0434</v>
       </c>
       <c r="J477" t="n">
-        <v>21.903</v>
+        <v>21.9114</v>
       </c>
     </row>
     <row r="478">
@@ -23355,10 +23355,10 @@
         <v>1.82</v>
       </c>
       <c r="I478" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.9294</v>
       </c>
       <c r="J478" t="n">
-        <v>19.5069</v>
+        <v>19.5174</v>
       </c>
     </row>
     <row r="479">
@@ -23392,13 +23392,13 @@
         <v>21</v>
       </c>
       <c r="H479" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I479" t="n">
-        <v>0.5789</v>
+        <v>0.5689</v>
       </c>
       <c r="J479" t="n">
-        <v>12.1569</v>
+        <v>11.9469</v>
       </c>
     </row>
     <row r="480">
@@ -23435,10 +23435,10 @@
         <v>0.54</v>
       </c>
       <c r="I480" t="n">
-        <v>-0.5039</v>
+        <v>-0.5038</v>
       </c>
       <c r="J480" t="n">
-        <v>-10.5819</v>
+        <v>-10.5798</v>
       </c>
     </row>
     <row r="481">
@@ -23475,10 +23475,10 @@
         <v>0.4</v>
       </c>
       <c r="I481" t="n">
-        <v>-0.6176</v>
+        <v>-0.6175</v>
       </c>
       <c r="J481" t="n">
-        <v>-12.9696</v>
+        <v>-12.9675</v>
       </c>
     </row>
     <row r="482">
@@ -25124,7 +25124,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -25484,7 +25484,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -25964,7 +25964,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -26912,13 +26912,13 @@
         <v>30</v>
       </c>
       <c r="H567" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I567" t="n">
-        <v>1.0311</v>
+        <v>1.0203</v>
       </c>
       <c r="J567" t="n">
-        <v>30.933</v>
+        <v>30.609</v>
       </c>
     </row>
     <row r="568">
@@ -26955,10 +26955,10 @@
         <v>1.13</v>
       </c>
       <c r="I568" t="n">
-        <v>0.3044</v>
+        <v>0.3047</v>
       </c>
       <c r="J568" t="n">
-        <v>9.132</v>
+        <v>9.141</v>
       </c>
     </row>
     <row r="569">
@@ -26995,10 +26995,10 @@
         <v>0.97</v>
       </c>
       <c r="I569" t="n">
-        <v>-0.0602</v>
+        <v>-0.0601</v>
       </c>
       <c r="J569" t="n">
-        <v>-1.806</v>
+        <v>-1.803</v>
       </c>
     </row>
     <row r="570">
@@ -27035,10 +27035,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I570" t="n">
-        <v>-0.245</v>
+        <v>-0.2448</v>
       </c>
       <c r="J570" t="n">
-        <v>-7.35</v>
+        <v>-7.344</v>
       </c>
     </row>
     <row r="571">
@@ -27075,10 +27075,10 @@
         <v>0.62</v>
       </c>
       <c r="I571" t="n">
-        <v>-0.4219</v>
+        <v>-0.4218</v>
       </c>
       <c r="J571" t="n">
-        <v>-12.657</v>
+        <v>-12.654</v>
       </c>
     </row>
     <row r="572">
@@ -30115,10 +30115,10 @@
         <v>1.78</v>
       </c>
       <c r="I647" t="n">
-        <v>0.8945</v>
+        <v>0.8941</v>
       </c>
       <c r="J647" t="n">
-        <v>20.5735</v>
+        <v>20.5643</v>
       </c>
     </row>
     <row r="648">
@@ -30155,10 +30155,10 @@
         <v>1.41</v>
       </c>
       <c r="I648" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5285</v>
       </c>
       <c r="J648" t="n">
-        <v>12.1601</v>
+        <v>12.1555</v>
       </c>
     </row>
     <row r="649">
@@ -30195,10 +30195,10 @@
         <v>1.21</v>
       </c>
       <c r="I649" t="n">
-        <v>0.3096</v>
+        <v>0.3095</v>
       </c>
       <c r="J649" t="n">
-        <v>7.1208</v>
+        <v>7.1185</v>
       </c>
     </row>
     <row r="650">
@@ -30232,13 +30232,13 @@
         <v>23</v>
       </c>
       <c r="H650" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I650" t="n">
-        <v>0.0348</v>
+        <v>0.0547</v>
       </c>
       <c r="J650" t="n">
-        <v>0.8004</v>
+        <v>1.2581</v>
       </c>
     </row>
     <row r="651">
@@ -30275,10 +30275,10 @@
         <v>0.7</v>
       </c>
       <c r="I651" t="n">
-        <v>-0.3646</v>
+        <v>-0.3648</v>
       </c>
       <c r="J651" t="n">
-        <v>-8.3858</v>
+        <v>-8.3904</v>
       </c>
     </row>
     <row r="652">
@@ -31912,13 +31912,13 @@
         <v>17</v>
       </c>
       <c r="H692" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="I692" t="n">
-        <v>1.7501</v>
+        <v>1.7189</v>
       </c>
       <c r="J692" t="n">
-        <v>29.7517</v>
+        <v>29.2213</v>
       </c>
     </row>
     <row r="693">
@@ -31952,13 +31952,13 @@
         <v>17</v>
       </c>
       <c r="H693" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I693" t="n">
-        <v>1.1629</v>
+        <v>1.1522</v>
       </c>
       <c r="J693" t="n">
-        <v>19.7693</v>
+        <v>19.5874</v>
       </c>
     </row>
     <row r="694">
@@ -31992,13 +31992,13 @@
         <v>17</v>
       </c>
       <c r="H694" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="I694" t="n">
-        <v>0.8991</v>
+        <v>0.8822</v>
       </c>
       <c r="J694" t="n">
-        <v>15.2847</v>
+        <v>14.9974</v>
       </c>
     </row>
     <row r="695">
@@ -32032,13 +32032,13 @@
         <v>17</v>
       </c>
       <c r="H695" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="I695" t="n">
-        <v>0.2523</v>
+        <v>0.1994</v>
       </c>
       <c r="J695" t="n">
-        <v>4.2891</v>
+        <v>3.3898</v>
       </c>
     </row>
     <row r="696">
@@ -32072,13 +32072,13 @@
         <v>17</v>
       </c>
       <c r="H696" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="I696" t="n">
-        <v>-0.463</v>
+        <v>-0.486</v>
       </c>
       <c r="J696" t="n">
-        <v>-7.871</v>
+        <v>-8.262</v>
       </c>
     </row>
     <row r="697">
@@ -32112,13 +32112,13 @@
         <v>17</v>
       </c>
       <c r="H697" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I697" t="n">
-        <v>0.1527</v>
+        <v>0.1759</v>
       </c>
       <c r="J697" t="n">
-        <v>2.5959</v>
+        <v>2.9903</v>
       </c>
     </row>
     <row r="698">
@@ -32152,13 +32152,13 @@
         <v>17</v>
       </c>
       <c r="H698" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I698" t="n">
-        <v>-0.1497</v>
+        <v>-0.1395</v>
       </c>
       <c r="J698" t="n">
-        <v>-2.5449</v>
+        <v>-2.3715</v>
       </c>
     </row>
     <row r="699">
@@ -32195,10 +32195,10 @@
         <v>0.85</v>
       </c>
       <c r="I699" t="n">
-        <v>-0.1825</v>
+        <v>-0.1835</v>
       </c>
       <c r="J699" t="n">
-        <v>-3.1025</v>
+        <v>-3.1195</v>
       </c>
     </row>
     <row r="700">
@@ -32232,13 +32232,13 @@
         <v>17</v>
       </c>
       <c r="H700" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="I700" t="n">
-        <v>-0.3711</v>
+        <v>-0.3629</v>
       </c>
       <c r="J700" t="n">
-        <v>-6.3087</v>
+        <v>-6.1693</v>
       </c>
     </row>
     <row r="701">
@@ -32272,13 +32272,13 @@
         <v>17</v>
       </c>
       <c r="H701" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I701" t="n">
-        <v>-0.5037</v>
+        <v>-0.4958</v>
       </c>
       <c r="J701" t="n">
-        <v>-8.562900000000001</v>
+        <v>-8.428599999999999</v>
       </c>
     </row>
     <row r="702">
@@ -32712,13 +32712,13 @@
         <v>21</v>
       </c>
       <c r="H712" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I712" t="n">
-        <v>1.4388</v>
+        <v>1.4267</v>
       </c>
       <c r="J712" t="n">
-        <v>30.2148</v>
+        <v>29.9607</v>
       </c>
     </row>
     <row r="713">
@@ -32755,10 +32755,10 @@
         <v>1.51</v>
       </c>
       <c r="I713" t="n">
-        <v>1.1015</v>
+        <v>1.1019</v>
       </c>
       <c r="J713" t="n">
-        <v>23.1315</v>
+        <v>23.1399</v>
       </c>
     </row>
     <row r="714">
@@ -32795,10 +32795,10 @@
         <v>1.19</v>
       </c>
       <c r="I714" t="n">
-        <v>0.5127</v>
+        <v>0.513</v>
       </c>
       <c r="J714" t="n">
-        <v>10.7667</v>
+        <v>10.773</v>
       </c>
     </row>
     <row r="715">
@@ -32835,10 +32835,10 @@
         <v>1.05</v>
       </c>
       <c r="I715" t="n">
-        <v>0.1553</v>
+        <v>0.1557</v>
       </c>
       <c r="J715" t="n">
-        <v>3.2613</v>
+        <v>3.2697</v>
       </c>
     </row>
     <row r="716">
@@ -32875,10 +32875,10 @@
         <v>0.9</v>
       </c>
       <c r="I716" t="n">
-        <v>-0.3942</v>
+        <v>-0.3939</v>
       </c>
       <c r="J716" t="n">
-        <v>-8.2782</v>
+        <v>-8.2719</v>
       </c>
     </row>
     <row r="717">
@@ -32915,10 +32915,10 @@
         <v>1.36</v>
       </c>
       <c r="I717" t="n">
-        <v>0.7425</v>
+        <v>0.7416</v>
       </c>
       <c r="J717" t="n">
-        <v>15.5925</v>
+        <v>15.5736</v>
       </c>
     </row>
     <row r="718">
@@ -32952,13 +32952,13 @@
         <v>21</v>
       </c>
       <c r="H718" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I718" t="n">
-        <v>-0.1012</v>
+        <v>-0.0888</v>
       </c>
       <c r="J718" t="n">
-        <v>-2.1252</v>
+        <v>-1.8648</v>
       </c>
     </row>
     <row r="719">
@@ -32995,10 +32995,10 @@
         <v>0.82</v>
       </c>
       <c r="I719" t="n">
-        <v>-0.2198</v>
+        <v>-0.2199</v>
       </c>
       <c r="J719" t="n">
-        <v>-4.6158</v>
+        <v>-4.6179</v>
       </c>
     </row>
     <row r="720">
@@ -33035,10 +33035,10 @@
         <v>0.61</v>
       </c>
       <c r="I720" t="n">
-        <v>-0.4159</v>
+        <v>-0.4161</v>
       </c>
       <c r="J720" t="n">
-        <v>-8.7339</v>
+        <v>-8.738099999999999</v>
       </c>
     </row>
     <row r="721">
@@ -33075,10 +33075,10 @@
         <v>0.6</v>
       </c>
       <c r="I721" t="n">
-        <v>-0.4248</v>
+        <v>-0.425</v>
       </c>
       <c r="J721" t="n">
-        <v>-8.9208</v>
+        <v>-8.925000000000001</v>
       </c>
     </row>
     <row r="722">
@@ -33284,7 +33284,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -33512,13 +33512,13 @@
         <v>15</v>
       </c>
       <c r="H732" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="I732" t="n">
-        <v>1.8874</v>
+        <v>1.8763</v>
       </c>
       <c r="J732" t="n">
-        <v>28.311</v>
+        <v>28.1445</v>
       </c>
     </row>
     <row r="733">
@@ -33592,13 +33592,13 @@
         <v>15</v>
       </c>
       <c r="H734" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="I734" t="n">
-        <v>1.0417</v>
+        <v>1.0688</v>
       </c>
       <c r="J734" t="n">
-        <v>15.6255</v>
+        <v>16.032</v>
       </c>
     </row>
     <row r="735">
@@ -33632,13 +33632,13 @@
         <v>15</v>
       </c>
       <c r="H735" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="I735" t="n">
-        <v>0.9125</v>
+        <v>0.8185</v>
       </c>
       <c r="J735" t="n">
-        <v>13.6875</v>
+        <v>12.2775</v>
       </c>
     </row>
     <row r="736">
@@ -33672,13 +33672,13 @@
         <v>15</v>
       </c>
       <c r="H736" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="I736" t="n">
-        <v>0.4453</v>
+        <v>0.5341</v>
       </c>
       <c r="J736" t="n">
-        <v>6.6795</v>
+        <v>8.0115</v>
       </c>
     </row>
     <row r="737">
@@ -33712,13 +33712,13 @@
         <v>15</v>
       </c>
       <c r="H737" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I737" t="n">
-        <v>-0.1454</v>
+        <v>-0.1619</v>
       </c>
       <c r="J737" t="n">
-        <v>-2.181</v>
+        <v>-2.4285</v>
       </c>
     </row>
     <row r="738">
@@ -33752,13 +33752,13 @@
         <v>15</v>
       </c>
       <c r="H738" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="I738" t="n">
-        <v>-0.2866</v>
+        <v>-0.2175</v>
       </c>
       <c r="J738" t="n">
-        <v>-4.299</v>
+        <v>-3.2625</v>
       </c>
     </row>
     <row r="739">
@@ -33795,16 +33795,16 @@
         <v>0.57</v>
       </c>
       <c r="I739" t="n">
-        <v>-0.416</v>
+        <v>-0.4174</v>
       </c>
       <c r="J739" t="n">
-        <v>-6.24</v>
+        <v>-6.261</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -33832,19 +33832,19 @@
         <v>15</v>
       </c>
       <c r="H740" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="I740" t="n">
-        <v>-0.5641</v>
+        <v>-0.5839</v>
       </c>
       <c r="J740" t="n">
-        <v>-8.461499999999999</v>
+        <v>-8.7585</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -33872,13 +33872,13 @@
         <v>15</v>
       </c>
       <c r="H741" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="I741" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.5928</v>
       </c>
       <c r="J741" t="n">
-        <v>-9.260999999999999</v>
+        <v>-8.891999999999999</v>
       </c>
     </row>
     <row r="742">
